--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>06/24 12:36:33</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>180000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>21428.57</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>马瑞昭</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>06/24 12:08:55</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>24096.39</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>羊美云</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>200000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>380000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45524.96</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>24096.39</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>45524.96</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
@@ -241,59 +241,86 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>06/24 14:10:57</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>45524</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>380000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>45524.96</t>
+          <t>380000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45524.96</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>45524</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>45524.96</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.96</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/24 12:36:33</t>
+          <t>06/25 16:34:17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,17 +90,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>21428.57</t>
+          <t>48192.77</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -117,210 +117,252 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>06/24 12:36:33</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>180000</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>21428.57</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>马瑞昭</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>06/24 12:08:55</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>24096.39</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>羊美云</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>标记人</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>操作人</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>06/24 14:10:57</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>45524</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>380000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>45524.96</t>
+          <t>780000</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>45524</t>
+          <t>93717.73</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>45524</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.96</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>48193.73</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
@@ -286,83 +286,110 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>06/25 19:22:04</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>48192</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>06/24 14:10:57</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>45524</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>780000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>93717.73</t>
+          <t>780000</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>45524</t>
+          <t>93717.73</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>93716</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>48193.73</t>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1.73</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/25 16:34:17</t>
+          <t>06/26 14:40:59</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,17 +90,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>48192.77</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06/24 12:36:33</t>
+          <t>06/25 16:34:17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,17 +132,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>21428.57</t>
+          <t>48192.77</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -159,237 +159,279 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>06/24 12:36:33</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>180000</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>21428.57</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>马瑞昭</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>06/24 12:08:55</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>24096.39</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>羊美云</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>06/25 19:22:04</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>48192</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>06/25 19:22:04</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>48192</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>06/24 14:10:57</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>45524</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>780000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>93717.73</t>
+          <t>880000</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>93716</t>
+          <t>105622.49</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>93716</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1.73</t>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>11906.49</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
@@ -328,12 +328,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06/25 19:22:04</t>
+          <t>06/26 16:07:20</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>48192</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -355,83 +355,110 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>06/25 19:22:04</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>48192</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>06/24 14:10:57</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>45524</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>880000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>105622.49</t>
+          <t>880000</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>93716</t>
+          <t>105622.49</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>105620</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>11906.49</t>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2.49</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/26 14:40:59</t>
+          <t>06/27 11:42:49</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06/25 16:34:17</t>
+          <t>06/26 14:40:59</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,17 +132,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>48192.77</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>06/24 12:36:33</t>
+          <t>06/25 16:34:17</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,17 +174,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>21428.57</t>
+          <t>48192.77</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -201,166 +201,181 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>06/24 12:36:33</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>180000</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>21428.57</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>马瑞昭</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>06/24 12:08:55</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>24096.39</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>羊美云</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06/26 16:07:20</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06/25 19:22:04</t>
+          <t>06/26 16:07:20</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>48192</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -382,83 +397,110 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>06/25 19:22:04</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>48192</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>06/24 14:10:57</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>45524</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>880000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>105622.49</t>
+          <t>1180000</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>105620</t>
+          <t>141767.07</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>105620</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2.49</t>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>36147.07</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/27 11:42:49</t>
+          <t>06/27 13:03:05</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>6172.84</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06/26 14:40:59</t>
+          <t>06/27 11:42:49</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>06/25 16:34:17</t>
+          <t>06/26 14:40:59</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,17 +174,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>48192.77</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>06/24 12:36:33</t>
+          <t>06/25 16:34:17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,17 +216,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>21428.57</t>
+          <t>48192.77</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -243,166 +243,181 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>06/24 12:36:33</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>180000</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>21428.57</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>马瑞昭</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>06/24 12:08:55</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>24096.39</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>羊美云</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06/26 16:07:20</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06/25 19:22:04</t>
+          <t>06/26 16:07:20</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>48192</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -424,83 +439,110 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>06/25 19:22:04</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>48192</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>06/24 14:10:57</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>45524</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1180000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>141767.07</t>
+          <t>1230000</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>105620</t>
+          <t>147939.91</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>105620</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>36147.07</t>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>42319.91</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
@@ -412,12 +412,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06/26 16:07:20</t>
+          <t>06/27 13:07:43</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>42317</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -427,7 +427,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -439,12 +439,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06/25 19:22:04</t>
+          <t>06/26 16:07:20</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>48192</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -466,83 +466,110 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>06/25 19:22:04</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>48192</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>06/24 14:10:57</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>45524</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>1230000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>147939.91</t>
+          <t>1230000</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>105620</t>
+          <t>147939.91</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>147937</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>42319.91</t>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2.91</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/27 13:03:05</t>
+          <t>06/29 12:46:37</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,17 +90,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>6172.84</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t/>
+          <t>林伟超</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06/27 11:42:49</t>
+          <t>06/27 13:03:05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>6172.84</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>06/26 14:40:59</t>
+          <t>06/27 11:42:49</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>06/25 16:34:17</t>
+          <t>06/26 14:40:59</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,17 +216,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>48192.77</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>06/24 12:36:33</t>
+          <t>06/25 16:34:17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,17 +258,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>21428.57</t>
+          <t>48192.77</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -285,166 +285,181 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>06/24 12:36:33</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>180000</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>21428.57</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>马瑞昭</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>06/24 12:08:55</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>24096.39</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>羊美云</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06/27 13:07:43</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>42317</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06/26 16:07:20</t>
+          <t>06/27 13:07:43</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>42317</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -454,7 +469,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -466,12 +481,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06/25 19:22:04</t>
+          <t>06/26 16:07:20</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>48192</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -493,83 +508,110 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>06/25 19:22:04</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>48192</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>06/24 14:10:57</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>45524</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>1230000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>147939.91</t>
+          <t>1430000</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>147937</t>
+          <t>172036.29</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>147937</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2.91</t>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>24099.29</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
@@ -454,12 +454,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06/27 13:07:43</t>
+          <t>06/29 14:04:21</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>42317</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -469,7 +469,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -481,12 +481,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06/26 16:07:20</t>
+          <t>06/27 13:07:43</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>42317</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -496,7 +496,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -508,12 +508,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06/25 19:22:04</t>
+          <t>06/26 16:07:20</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>48192</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -535,83 +535,110 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>06/25 19:22:04</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>48192</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>06/24 14:10:57</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>45524</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>1430000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>172036.29</t>
+          <t>1430000</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>147937</t>
+          <t>172036.29</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>172033</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>24099.29</t>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>3.29</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/29 12:46:37</t>
+          <t>06/30 10:08:02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,12 +95,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>林伟超</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06/27 13:03:05</t>
+          <t>06/29 12:46:37</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,17 +132,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>6172.84</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t/>
+          <t>林伟超</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>06/27 11:42:49</t>
+          <t>06/27 13:03:05</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>6172.84</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>06/26 14:40:59</t>
+          <t>06/27 11:42:49</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>06/25 16:34:17</t>
+          <t>06/26 14:40:59</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,17 +258,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>48192.77</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>06/24 12:36:33</t>
+          <t>06/25 16:34:17</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,17 +300,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>21428.57</t>
+          <t>48192.77</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -327,166 +327,181 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>06/24 12:36:33</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>180000</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>21428.57</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>马瑞昭</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>06/24 12:08:55</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>24096.39</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>羊美云</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06/29 14:04:21</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06/27 13:07:43</t>
+          <t>06/29 14:04:21</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>42317</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -496,7 +511,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -508,12 +523,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06/26 16:07:20</t>
+          <t>06/27 13:07:43</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>42317</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -523,7 +538,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -535,12 +550,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06/25 19:22:04</t>
+          <t>06/26 16:07:20</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>48192</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -562,83 +577,110 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>06/25 19:22:04</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>48192</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>06/24 14:10:57</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>45524</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>1430000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>172036.29</t>
+          <t>1930000</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>172033</t>
+          <t>232277.26</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>172033</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>3.29</t>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>60244.26</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/30 10:08:02</t>
+          <t>06/30 10:22:52</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,17 +90,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>114634.15</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06/29 12:46:37</t>
+          <t>06/30 10:08:02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,12 +137,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>林伟超</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>06/27 13:03:05</t>
+          <t>06/29 12:46:37</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,17 +174,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>6172.84</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t/>
+          <t>林伟超</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>06/27 11:42:49</t>
+          <t>06/27 13:03:05</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>6172.84</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>06/26 14:40:59</t>
+          <t>06/27 11:42:49</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>06/25 16:34:17</t>
+          <t>06/26 14:40:59</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,17 +300,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>48192.77</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>06/24 12:36:33</t>
+          <t>06/25 16:34:17</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,17 +342,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>21428.57</t>
+          <t>48192.77</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -369,166 +369,181 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>06/24 12:36:33</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>180000</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>21428.57</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>马瑞昭</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>06/24 12:08:55</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>24096.39</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>羊美云</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06/29 14:04:21</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06/27 13:07:43</t>
+          <t>06/29 14:04:21</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>42317</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -538,7 +553,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -550,12 +565,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06/26 16:07:20</t>
+          <t>06/27 13:07:43</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>42317</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -565,7 +580,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -577,12 +592,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06/25 19:22:04</t>
+          <t>06/26 16:07:20</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>48192</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -604,83 +619,110 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>06/25 19:22:04</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>48192</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>06/24 14:10:57</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>45524</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>1930000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>232277.26</t>
+          <t>2870000</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>172033</t>
+          <t>346911.4</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>172033</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>60244.26</t>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>174878.4</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/30 10:22:52</t>
+          <t>06/30 10:47:16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,17 +90,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>114634.15</t>
+          <t>33734.94</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t/>
+          <t>耿振云</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06/30 10:08:02</t>
+          <t>06/30 10:22:52</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,17 +132,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>114634.15</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>06/29 12:46:37</t>
+          <t>06/30 10:08:02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,12 +179,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>林伟超</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>06/27 13:03:05</t>
+          <t>06/29 12:46:37</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,17 +216,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>6172.84</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t/>
+          <t>林伟超</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>06/27 11:42:49</t>
+          <t>06/27 13:03:05</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>6172.84</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>06/26 14:40:59</t>
+          <t>06/27 11:42:49</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>06/25 16:34:17</t>
+          <t>06/26 14:40:59</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,17 +342,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>48192.77</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>06/24 12:36:33</t>
+          <t>06/25 16:34:17</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,17 +384,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>21428.57</t>
+          <t>48192.77</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -411,166 +411,181 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>06/24 12:36:33</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>180000</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>21428.57</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>马瑞昭</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>06/24 12:08:55</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>24096.39</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>羊美云</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06/29 14:04:21</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06/27 13:07:43</t>
+          <t>06/29 14:04:21</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>42317</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -580,7 +595,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -592,12 +607,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06/26 16:07:20</t>
+          <t>06/27 13:07:43</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>42317</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -607,7 +622,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -619,12 +634,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06/25 19:22:04</t>
+          <t>06/26 16:07:20</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>48192</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -646,83 +661,110 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>06/25 19:22:04</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>48192</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>06/24 14:10:57</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>45524</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2870000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>346911.4</t>
+          <t>3150000</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>172033</t>
+          <t>380646.34</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>172033</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>174878.4</t>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>208613.34</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
@@ -580,12 +580,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06/29 14:04:21</t>
+          <t>06/30 11:35:36</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>79000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -607,12 +607,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06/27 13:07:43</t>
+          <t>06/29 14:04:21</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>42317</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -634,12 +634,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06/26 16:07:20</t>
+          <t>06/27 13:07:43</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>42317</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -661,12 +661,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06/25 19:22:04</t>
+          <t>06/26 16:07:20</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>48192</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -688,83 +688,110 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>06/25 19:22:04</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>48192</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>06/24 14:10:57</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>45524</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>3150000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>380646.34</t>
+          <t>3150000</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>172033</t>
+          <t>380646.34</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>251033</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>208613.34</t>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>129613.34</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
@@ -580,12 +580,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06/30 11:35:36</t>
+          <t>06/30 11:50:16</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>79000</t>
+          <t>61000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -607,12 +607,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06/29 14:04:21</t>
+          <t>06/30 11:35:36</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>79000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -634,12 +634,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06/27 13:07:43</t>
+          <t>06/29 14:04:21</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>42317</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -661,12 +661,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06/26 16:07:20</t>
+          <t>06/27 13:07:43</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>42317</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -688,12 +688,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06/25 19:22:04</t>
+          <t>06/26 16:07:20</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>48192</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -715,83 +715,110 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>06/25 19:22:04</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>48192</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>06/24 14:10:57</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>45524</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>3150000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>380646.34</t>
+          <t>3150000</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>251033</t>
+          <t>380646.34</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>312033</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>129613.34</t>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>68613.34</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
@@ -580,12 +580,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06/30 11:50:16</t>
+          <t>06/30 12:16:11</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>61000</t>
+          <t>68610</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -607,12 +607,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06/30 11:35:36</t>
+          <t>06/30 11:50:16</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>79000</t>
+          <t>61000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -634,12 +634,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06/29 14:04:21</t>
+          <t>06/30 11:35:36</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>79000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -661,12 +661,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06/27 13:07:43</t>
+          <t>06/29 14:04:21</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>42317</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -688,12 +688,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06/26 16:07:20</t>
+          <t>06/27 13:07:43</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>42317</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -715,12 +715,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06/25 19:22:04</t>
+          <t>06/26 16:07:20</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>48192</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -742,83 +742,110 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>06/25 19:22:04</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>48192</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>06/24 14:10:57</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>45524</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>3150000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>380646.34</t>
+          <t>3150000</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>312033</t>
+          <t>380646.34</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>380643</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>68613.34</t>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>3.34</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/30 10:47:16</t>
+          <t>06/30 13:00:19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,12 +95,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>33734.94</t>
+          <t>38554.22</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>耿振云</t>
+          <t>李志伟</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06/30 10:22:52</t>
+          <t>06/30 10:47:16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,17 +132,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>114634.15</t>
+          <t>33734.94</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t/>
+          <t>耿振云</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>06/30 10:08:02</t>
+          <t>06/30 10:22:52</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,17 +174,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>114634.15</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>06/29 12:46:37</t>
+          <t>06/30 10:08:02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,12 +221,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>林伟超</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>06/27 13:03:05</t>
+          <t>06/29 12:46:37</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,17 +258,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>6172.84</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t/>
+          <t>林伟超</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>06/27 11:42:49</t>
+          <t>06/27 13:03:05</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>6172.84</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>06/26 14:40:59</t>
+          <t>06/27 11:42:49</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>06/25 16:34:17</t>
+          <t>06/26 14:40:59</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,17 +384,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>48192.77</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>06/24 12:36:33</t>
+          <t>06/25 16:34:17</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,17 +426,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>21428.57</t>
+          <t>48192.77</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -453,166 +453,181 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>06/24 12:36:33</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>180000</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>21428.57</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>马瑞昭</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>06/24 12:08:55</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>24096.39</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>羊美云</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06/30 12:16:11</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>68610</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06/30 11:50:16</t>
+          <t>06/30 12:16:11</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>61000</t>
+          <t>68610</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -622,7 +637,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -634,12 +649,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06/30 11:35:36</t>
+          <t>06/30 11:50:16</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>79000</t>
+          <t>61000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -661,12 +676,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06/29 14:04:21</t>
+          <t>06/30 11:35:36</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>79000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -688,12 +703,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06/27 13:07:43</t>
+          <t>06/29 14:04:21</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>42317</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -703,7 +718,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -715,12 +730,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06/26 16:07:20</t>
+          <t>06/27 13:07:43</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>42317</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -730,7 +745,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -742,12 +757,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06/25 19:22:04</t>
+          <t>06/26 16:07:20</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>48192</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -769,83 +784,110 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>06/25 19:22:04</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>48192</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>06/24 14:10:57</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>45524</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>3150000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>380646.34</t>
+          <t>3470000</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>380643</t>
+          <t>419200.56</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>380643</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>3.34</t>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>38557.56</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/30 13:00:19</t>
+          <t>06/30 13:54:57</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,12 +95,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>38554.22</t>
+          <t>33734.94</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>李志伟</t>
+          <t>马瑞昭</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06/30 10:47:16</t>
+          <t>06/30 13:00:19</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,12 +137,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>33734.94</t>
+          <t>38554.22</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>耿振云</t>
+          <t>李志伟</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>06/30 10:22:52</t>
+          <t>06/30 10:47:16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,17 +174,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>114634.15</t>
+          <t>33734.94</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t/>
+          <t>耿振云</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>06/30 10:08:02</t>
+          <t>06/30 10:22:52</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,17 +216,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>114634.15</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>06/29 12:46:37</t>
+          <t>06/30 10:08:02</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,12 +263,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>林伟超</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>06/27 13:03:05</t>
+          <t>06/29 12:46:37</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,17 +300,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>6172.84</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t/>
+          <t>林伟超</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>06/27 11:42:49</t>
+          <t>06/27 13:03:05</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>6172.84</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>06/26 14:40:59</t>
+          <t>06/27 11:42:49</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>06/25 16:34:17</t>
+          <t>06/26 14:40:59</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,17 +426,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>48192.77</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>06/24 12:36:33</t>
+          <t>06/25 16:34:17</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,17 +468,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>21428.57</t>
+          <t>48192.77</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -495,166 +495,181 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>06/24 12:36:33</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>180000</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>21428.57</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>马瑞昭</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>06/24 12:08:55</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>24096.39</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>羊美云</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06/30 12:16:11</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>68610</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06/30 11:50:16</t>
+          <t>06/30 12:16:11</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>61000</t>
+          <t>68610</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -664,7 +679,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -676,12 +691,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06/30 11:35:36</t>
+          <t>06/30 11:50:16</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>79000</t>
+          <t>61000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -703,12 +718,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06/29 14:04:21</t>
+          <t>06/30 11:35:36</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>79000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -730,12 +745,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06/27 13:07:43</t>
+          <t>06/29 14:04:21</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>42317</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -745,7 +760,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -757,12 +772,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06/26 16:07:20</t>
+          <t>06/27 13:07:43</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>42317</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -772,7 +787,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -784,12 +799,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06/25 19:22:04</t>
+          <t>06/26 16:07:20</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>48192</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -811,83 +826,110 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>06/25 19:22:04</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>48192</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>06/24 14:10:57</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>45524</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>3470000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>419200.56</t>
+          <t>3750000</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>380643</t>
+          <t>452935.5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>380643</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>38557.56</t>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>72292.5</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
@@ -664,12 +664,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06/30 12:16:11</t>
+          <t>06/30 15:16:34</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>68610</t>
+          <t>72289</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -691,12 +691,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06/30 11:50:16</t>
+          <t>06/30 12:16:11</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>61000</t>
+          <t>68610</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -718,12 +718,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06/30 11:35:36</t>
+          <t>06/30 11:50:16</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>79000</t>
+          <t>61000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -745,12 +745,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06/29 14:04:21</t>
+          <t>06/30 11:35:36</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>79000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -772,12 +772,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06/27 13:07:43</t>
+          <t>06/29 14:04:21</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>42317</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -799,12 +799,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06/26 16:07:20</t>
+          <t>06/27 13:07:43</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>42317</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -826,12 +826,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06/25 19:22:04</t>
+          <t>06/26 16:07:20</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>48192</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -853,83 +853,110 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>06/25 19:22:04</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>48192</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>06/24 14:10:57</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>45524</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>3750000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>452935.5</t>
+          <t>3750000</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>380643</t>
+          <t>452935.5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>452932</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>72292.5</t>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>3.5</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/30 13:54:57</t>
+          <t>07/01 14:50:11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,17 +95,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>33734.94</t>
+          <t>46987.95</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>向文</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06/30 13:00:19</t>
+          <t>06/30 13:54:57</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,12 +137,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>38554.22</t>
+          <t>33734.94</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>李志伟</t>
+          <t>马瑞昭</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>06/30 10:47:16</t>
+          <t>06/30 13:00:19</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,12 +179,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>33734.94</t>
+          <t>38554.22</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>耿振云</t>
+          <t>李志伟</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>06/30 10:22:52</t>
+          <t>06/30 10:47:16</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,17 +216,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>114634.15</t>
+          <t>33734.94</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t/>
+          <t>耿振云</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>06/30 10:08:02</t>
+          <t>06/30 10:22:52</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,17 +258,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>114634.15</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>06/29 12:46:37</t>
+          <t>06/30 10:08:02</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,12 +305,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>林伟超</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>06/27 13:03:05</t>
+          <t>06/29 12:46:37</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,17 +342,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>6172.84</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t/>
+          <t>林伟超</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>06/27 11:42:49</t>
+          <t>06/27 13:03:05</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>6172.84</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>06/26 14:40:59</t>
+          <t>06/27 11:42:49</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>06/25 16:34:17</t>
+          <t>06/26 14:40:59</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,17 +468,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>48192.77</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06/24 12:36:33</t>
+          <t>06/25 16:34:17</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,17 +510,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>21428.57</t>
+          <t>48192.77</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -537,166 +537,181 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>06/24 12:36:33</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>180000</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>21428.57</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>马瑞昭</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>06/24 12:08:55</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>24096.39</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>羊美云</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06/30 15:16:34</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>72289</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06/30 12:16:11</t>
+          <t>06/30 15:16:34</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>68610</t>
+          <t>72289</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -706,7 +721,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -718,12 +733,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06/30 11:50:16</t>
+          <t>06/30 12:16:11</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>61000</t>
+          <t>68610</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -733,7 +748,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -745,12 +760,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06/30 11:35:36</t>
+          <t>06/30 11:50:16</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>79000</t>
+          <t>61000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -772,12 +787,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06/29 14:04:21</t>
+          <t>06/30 11:35:36</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>79000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -799,12 +814,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06/27 13:07:43</t>
+          <t>06/29 14:04:21</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>42317</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -814,7 +829,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -826,12 +841,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06/26 16:07:20</t>
+          <t>06/27 13:07:43</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>42317</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -841,7 +856,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -853,12 +868,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06/25 19:22:04</t>
+          <t>06/26 16:07:20</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>48192</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -880,83 +895,110 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>06/25 19:22:04</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>48192</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>06/24 14:10:57</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>45524</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>3750000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>452935.5</t>
+          <t>4140000</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>452932</t>
+          <t>499923.45</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>452932</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>3.5</t>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>46991.45</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/01 14:50:11</t>
+          <t>07/01 15:40:01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,17 +95,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>46987.95</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>向文</t>
+          <t>林伟超</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06/30 13:54:57</t>
+          <t>07/01 14:50:11</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,17 +137,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>33734.94</t>
+          <t>46987.95</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>向文</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>06/30 13:00:19</t>
+          <t>06/30 13:54:57</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,12 +179,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>38554.22</t>
+          <t>33734.94</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>李志伟</t>
+          <t>马瑞昭</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>06/30 10:47:16</t>
+          <t>06/30 13:00:19</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,12 +221,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>33734.94</t>
+          <t>38554.22</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>耿振云</t>
+          <t>李志伟</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>06/30 10:22:52</t>
+          <t>06/30 10:47:16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,17 +258,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>114634.15</t>
+          <t>33734.94</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t/>
+          <t>耿振云</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>06/30 10:08:02</t>
+          <t>06/30 10:22:52</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,17 +300,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>114634.15</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>06/29 12:46:37</t>
+          <t>06/30 10:08:02</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,12 +347,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>林伟超</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>06/27 13:03:05</t>
+          <t>06/29 12:46:37</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,17 +384,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>6172.84</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t/>
+          <t>林伟超</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>06/27 11:42:49</t>
+          <t>06/27 13:03:05</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>6172.84</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>06/26 14:40:59</t>
+          <t>06/27 11:42:49</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06/25 16:34:17</t>
+          <t>06/26 14:40:59</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,17 +510,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>48192.77</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06/24 12:36:33</t>
+          <t>06/25 16:34:17</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,17 +552,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>21428.57</t>
+          <t>48192.77</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -579,166 +579,181 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>06/24 12:36:33</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>180000</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>21428.57</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>马瑞昭</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>06/24 12:08:55</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>24096.39</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>羊美云</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06/30 15:16:34</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>72289</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06/30 12:16:11</t>
+          <t>06/30 15:16:34</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>68610</t>
+          <t>72289</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -748,7 +763,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -760,12 +775,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06/30 11:50:16</t>
+          <t>06/30 12:16:11</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>61000</t>
+          <t>68610</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -775,7 +790,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -787,12 +802,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06/30 11:35:36</t>
+          <t>06/30 11:50:16</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>79000</t>
+          <t>61000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -814,12 +829,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06/29 14:04:21</t>
+          <t>06/30 11:35:36</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>79000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -841,12 +856,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06/27 13:07:43</t>
+          <t>06/29 14:04:21</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>42317</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -856,7 +871,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -868,12 +883,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06/26 16:07:20</t>
+          <t>06/27 13:07:43</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>42317</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -883,7 +898,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -895,12 +910,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06/25 19:22:04</t>
+          <t>06/26 16:07:20</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>48192</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -922,83 +937,110 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>06/25 19:22:04</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>48192</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>06/24 14:10:57</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>45524</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="33"/>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>4140000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>499923.45</t>
+          <t>4390000</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>452932</t>
+          <t>530043.93</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>452932</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>46991.45</t>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>77111.93</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
@@ -748,12 +748,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06/30 15:16:34</t>
+          <t>07/01 16:52:50</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>72289</t>
+          <t>77108</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -775,12 +775,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06/30 12:16:11</t>
+          <t>06/30 15:16:34</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>68610</t>
+          <t>72289</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -802,12 +802,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06/30 11:50:16</t>
+          <t>06/30 12:16:11</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>61000</t>
+          <t>68610</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -817,7 +817,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -829,12 +829,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06/30 11:35:36</t>
+          <t>06/30 11:50:16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>79000</t>
+          <t>61000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -856,12 +856,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06/29 14:04:21</t>
+          <t>06/30 11:35:36</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>79000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -883,12 +883,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06/27 13:07:43</t>
+          <t>06/29 14:04:21</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>42317</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -910,12 +910,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06/26 16:07:20</t>
+          <t>06/27 13:07:43</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>42317</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -925,7 +925,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -937,12 +937,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06/25 19:22:04</t>
+          <t>06/26 16:07:20</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>48192</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -964,83 +964,110 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>06/25 19:22:04</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>48192</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>06/24 14:10:57</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>45524</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="34"/>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>4390000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>530043.93</t>
+          <t>4390000</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>452932</t>
+          <t>530043.93</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>530040</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>77111.93</t>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>3.93</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/01 15:40:01</t>
+          <t>07/01 18:40:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,22 +90,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>林伟超</t>
+          <t>:安徽省阜阳市临泉县杨桥镇 安徽 明天 9.00</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>nn40007</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/01 14:50:11</t>
+          <t>07/01 15:40:01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,17 +137,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>46987.95</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>向文</t>
+          <t>林伟超</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>06/30 13:54:57</t>
+          <t>07/01 14:50:11</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,17 +179,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>33734.94</t>
+          <t>46987.95</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>向文</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>06/30 13:00:19</t>
+          <t>06/30 13:54:57</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,12 +221,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>38554.22</t>
+          <t>33734.94</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>李志伟</t>
+          <t>马瑞昭</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>06/30 10:47:16</t>
+          <t>06/30 13:00:19</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,12 +263,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>33734.94</t>
+          <t>38554.22</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>耿振云</t>
+          <t>李志伟</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>06/30 10:22:52</t>
+          <t>06/30 10:47:16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,17 +300,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>114634.15</t>
+          <t>33734.94</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t/>
+          <t>耿振云</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>06/30 10:08:02</t>
+          <t>06/30 10:22:52</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,17 +342,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>114634.15</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>06/29 12:46:37</t>
+          <t>06/30 10:08:02</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,12 +389,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>林伟超</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>06/27 13:03:05</t>
+          <t>06/29 12:46:37</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,17 +426,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>6172.84</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t/>
+          <t>林伟超</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>06/27 11:42:49</t>
+          <t>06/27 13:03:05</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>6172.84</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06/26 14:40:59</t>
+          <t>06/27 11:42:49</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06/25 16:34:17</t>
+          <t>06/26 14:40:59</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,17 +552,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>48192.77</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06/24 12:36:33</t>
+          <t>06/25 16:34:17</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,17 +594,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>21428.57</t>
+          <t>48192.77</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -621,166 +621,181 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>06/24 12:36:33</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>180000</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>21428.57</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>马瑞昭</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>06/24 12:08:55</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>24096.39</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>羊美云</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/01 16:52:50</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>77108</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06/30 15:16:34</t>
+          <t>07/01 16:52:50</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>72289</t>
+          <t>77108</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -802,12 +817,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06/30 12:16:11</t>
+          <t>06/30 15:16:34</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>68610</t>
+          <t>72289</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -817,7 +832,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -829,12 +844,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06/30 11:50:16</t>
+          <t>06/30 12:16:11</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>61000</t>
+          <t>68610</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -844,7 +859,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -856,12 +871,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06/30 11:35:36</t>
+          <t>06/30 11:50:16</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>79000</t>
+          <t>61000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -883,12 +898,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06/29 14:04:21</t>
+          <t>06/30 11:35:36</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>79000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -910,12 +925,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06/27 13:07:43</t>
+          <t>06/29 14:04:21</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>42317</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -925,7 +940,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -937,12 +952,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06/26 16:07:20</t>
+          <t>06/27 13:07:43</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>42317</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -952,7 +967,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -964,12 +979,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06/25 19:22:04</t>
+          <t>06/26 16:07:20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>48192</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -991,83 +1006,110 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>06/25 19:22:04</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>48192</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>06/24 14:10:57</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>45524</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="36"/>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>4390000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>530043.93</t>
+          <t>4389990</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>530040</t>
+          <t>530033.93</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>530040</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>3.93</t>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>-6.07</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/01 18:40:00</t>
+          <t>07/02 09:17:34</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,22 +90,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>27710.84</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 安徽 明天 9.00</t>
+          <t>王志宽</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>nn40007</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/01 15:40:01</t>
+          <t>07/01 18:40:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,22 +132,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>林伟超</t>
+          <t>:安徽省阜阳市临泉县杨桥镇 安徽 明天 9.00</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>nn40007</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/01 14:50:11</t>
+          <t>07/01 15:40:01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,17 +179,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>46987.95</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>向文</t>
+          <t>林伟超</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>06/30 13:54:57</t>
+          <t>07/01 14:50:11</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,17 +221,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>33734.94</t>
+          <t>46987.95</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>向文</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>06/30 13:00:19</t>
+          <t>06/30 13:54:57</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,12 +263,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>38554.22</t>
+          <t>33734.94</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>李志伟</t>
+          <t>马瑞昭</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>06/30 10:47:16</t>
+          <t>06/30 13:00:19</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,12 +305,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>33734.94</t>
+          <t>38554.22</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>耿振云</t>
+          <t>李志伟</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>06/30 10:22:52</t>
+          <t>06/30 10:47:16</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,17 +342,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>114634.15</t>
+          <t>33734.94</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t/>
+          <t>耿振云</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>06/30 10:08:02</t>
+          <t>06/30 10:22:52</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,17 +384,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>114634.15</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>06/29 12:46:37</t>
+          <t>06/30 10:08:02</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -431,12 +431,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>林伟超</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>06/27 13:03:05</t>
+          <t>06/29 12:46:37</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,17 +468,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>6172.84</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t/>
+          <t>林伟超</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06/27 11:42:49</t>
+          <t>06/27 13:03:05</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>6172.84</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06/26 14:40:59</t>
+          <t>06/27 11:42:49</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06/25 16:34:17</t>
+          <t>06/26 14:40:59</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,17 +594,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>48192.77</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06/24 12:36:33</t>
+          <t>06/25 16:34:17</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,17 +636,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>21428.57</t>
+          <t>48192.77</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -663,166 +663,181 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>06/24 12:36:33</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>180000</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>21428.57</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>马瑞昭</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>06/24 12:08:55</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>24096.39</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>羊美云</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/01 16:52:50</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>77108</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06/30 15:16:34</t>
+          <t>07/01 16:52:50</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>72289</t>
+          <t>77108</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -844,12 +859,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06/30 12:16:11</t>
+          <t>06/30 15:16:34</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>68610</t>
+          <t>72289</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -859,7 +874,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -871,12 +886,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06/30 11:50:16</t>
+          <t>06/30 12:16:11</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>61000</t>
+          <t>68610</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -886,7 +901,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -898,12 +913,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06/30 11:35:36</t>
+          <t>06/30 11:50:16</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>79000</t>
+          <t>61000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -925,12 +940,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06/29 14:04:21</t>
+          <t>06/30 11:35:36</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>79000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -952,12 +967,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06/27 13:07:43</t>
+          <t>06/29 14:04:21</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>42317</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -967,7 +982,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -979,12 +994,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06/26 16:07:20</t>
+          <t>06/27 13:07:43</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>42317</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -994,7 +1009,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1006,12 +1021,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06/25 19:22:04</t>
+          <t>06/26 16:07:20</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>48192</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1033,83 +1048,110 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>06/25 19:22:04</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>48192</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>06/24 14:10:57</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>45524</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="36"/>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>4389990</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>530033.93</t>
+          <t>4619990</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>530040</t>
+          <t>557744.78</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>530040</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>-6.07</t>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>27704.78</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
@@ -832,12 +832,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/01 16:52:50</t>
+          <t>07/02 12:32:59</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>77108</t>
+          <t>27710</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -859,12 +859,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06/30 15:16:34</t>
+          <t>07/01 16:52:50</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>72289</t>
+          <t>77108</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -886,12 +886,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06/30 12:16:11</t>
+          <t>06/30 15:16:34</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>68610</t>
+          <t>72289</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -913,12 +913,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06/30 11:50:16</t>
+          <t>06/30 12:16:11</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>61000</t>
+          <t>68610</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -940,12 +940,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06/30 11:35:36</t>
+          <t>06/30 11:50:16</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>79000</t>
+          <t>61000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -967,12 +967,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06/29 14:04:21</t>
+          <t>06/30 11:35:36</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>79000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -994,12 +994,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06/27 13:07:43</t>
+          <t>06/29 14:04:21</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>42317</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1021,12 +1021,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06/26 16:07:20</t>
+          <t>06/27 13:07:43</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>42317</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1048,12 +1048,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06/25 19:22:04</t>
+          <t>06/26 16:07:20</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>48192</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1075,83 +1075,110 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>06/25 19:22:04</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>48192</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>06/24 14:10:57</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>45524</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="37"/>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="38"/>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>4619990</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>557744.78</t>
+          <t>4619990</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>530040</t>
+          <t>557744.78</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>557750</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>27704.78</t>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>-5.22</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/02 09:17:34</t>
+          <t>07/02 15:47:40</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>1064400</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,17 +95,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>27710.84</t>
+          <t>128240.96</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>王志宽</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/01 18:40:00</t>
+          <t>07/02 09:17:34</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,22 +132,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>27710.84</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 安徽 明天 9.00</t>
+          <t>王志宽</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>nn40007</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/01 15:40:01</t>
+          <t>07/01 18:40:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,22 +174,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>林伟超</t>
+          <t>:安徽省阜阳市临泉县杨桥镇 安徽 明天 9.00</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>nn40007</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/01 14:50:11</t>
+          <t>07/01 15:40:01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,17 +221,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>46987.95</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>向文</t>
+          <t>林伟超</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>06/30 13:54:57</t>
+          <t>07/01 14:50:11</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,17 +263,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>33734.94</t>
+          <t>46987.95</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>向文</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>06/30 13:00:19</t>
+          <t>06/30 13:54:57</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,12 +305,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>38554.22</t>
+          <t>33734.94</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>李志伟</t>
+          <t>马瑞昭</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>06/30 10:47:16</t>
+          <t>06/30 13:00:19</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,12 +347,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>33734.94</t>
+          <t>38554.22</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>耿振云</t>
+          <t>李志伟</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>06/30 10:22:52</t>
+          <t>06/30 10:47:16</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,17 +384,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>114634.15</t>
+          <t>33734.94</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t/>
+          <t>耿振云</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>06/30 10:08:02</t>
+          <t>06/30 10:22:52</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,17 +426,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>114634.15</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>06/29 12:46:37</t>
+          <t>06/30 10:08:02</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -473,12 +473,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>林伟超</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06/27 13:03:05</t>
+          <t>06/29 12:46:37</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,17 +510,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>6172.84</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t/>
+          <t>林伟超</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06/27 11:42:49</t>
+          <t>06/27 13:03:05</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>6172.84</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06/26 14:40:59</t>
+          <t>06/27 11:42:49</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06/25 16:34:17</t>
+          <t>06/26 14:40:59</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,17 +636,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>48192.77</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06/24 12:36:33</t>
+          <t>06/25 16:34:17</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,17 +678,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>21428.57</t>
+          <t>48192.77</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -705,166 +705,181 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>06/24 12:36:33</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>180000</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>21428.57</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>马瑞昭</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>06/24 12:08:55</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>24096.39</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>羊美云</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/02 12:32:59</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/01 16:52:50</t>
+          <t>07/02 12:32:59</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>77108</t>
+          <t>27710</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -886,12 +901,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06/30 15:16:34</t>
+          <t>07/01 16:52:50</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>72289</t>
+          <t>77108</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -913,12 +928,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06/30 12:16:11</t>
+          <t>06/30 15:16:34</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>68610</t>
+          <t>72289</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -928,7 +943,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -940,12 +955,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06/30 11:50:16</t>
+          <t>06/30 12:16:11</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>61000</t>
+          <t>68610</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -955,7 +970,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -967,12 +982,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06/30 11:35:36</t>
+          <t>06/30 11:50:16</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>79000</t>
+          <t>61000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -994,12 +1009,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06/29 14:04:21</t>
+          <t>06/30 11:35:36</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>79000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1021,12 +1036,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06/27 13:07:43</t>
+          <t>06/29 14:04:21</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>42317</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1036,7 +1051,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1048,12 +1063,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06/26 16:07:20</t>
+          <t>06/27 13:07:43</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>42317</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1063,7 +1078,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1075,12 +1090,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06/25 19:22:04</t>
+          <t>06/26 16:07:20</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>48192</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1102,83 +1117,110 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>06/25 19:22:04</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>48192</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>06/24 14:10:57</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>45524</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="38"/>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>4619990</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>557744.78</t>
+          <t>5684390</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>557750</t>
+          <t>685985.74</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>557750</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>-5.22</t>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>128235.74</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
@@ -874,12 +874,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/02 12:32:59</t>
+          <t>07/02 19:00:39</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>128241</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -901,12 +901,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/01 16:52:50</t>
+          <t>07/02 12:32:59</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>77108</t>
+          <t>27710</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -928,12 +928,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06/30 15:16:34</t>
+          <t>07/01 16:52:50</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>72289</t>
+          <t>77108</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -955,12 +955,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06/30 12:16:11</t>
+          <t>06/30 15:16:34</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>68610</t>
+          <t>72289</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -982,12 +982,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06/30 11:50:16</t>
+          <t>06/30 12:16:11</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>61000</t>
+          <t>68610</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1009,12 +1009,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06/30 11:35:36</t>
+          <t>06/30 11:50:16</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>79000</t>
+          <t>61000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1036,12 +1036,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06/29 14:04:21</t>
+          <t>06/30 11:35:36</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>79000</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1063,12 +1063,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06/27 13:07:43</t>
+          <t>06/29 14:04:21</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>42317</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1090,12 +1090,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06/26 16:07:20</t>
+          <t>06/27 13:07:43</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>42317</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1117,12 +1117,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06/25 19:22:04</t>
+          <t>06/26 16:07:20</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>48192</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1144,83 +1144,110 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>06/25 19:22:04</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>48192</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>06/24 14:10:57</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>45524</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="39"/>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>5684390</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>685985.74</t>
+          <t>5684390</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>557750</t>
+          <t>685985.74</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>685991</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>128235.74</t>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>-5.26</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/02 15:47:40</t>
+          <t>07/03 20:29:29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1064400</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,39 +90,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>128240.96</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t>上海浦东新区 明天上午11</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>moucai1111</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t/>
+          <t>17万 问</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/02 09:17:34</t>
+          <t>07/02 15:47:40</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>1064400</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,17 +137,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>27710.84</t>
+          <t>128240.96</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>王志宽</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/01 18:40:00</t>
+          <t>07/02 09:17:34</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,22 +174,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>27710.84</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 安徽 明天 9.00</t>
+          <t>王志宽</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>nn40007</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/01 15:40:01</t>
+          <t>07/01 18:40:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,22 +216,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>林伟超</t>
+          <t>:安徽省阜阳市临泉县杨桥镇 安徽 明天 9.00</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>nn40007</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/01 14:50:11</t>
+          <t>07/01 15:40:01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,17 +263,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>46987.95</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>向文</t>
+          <t>林伟超</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>06/30 13:54:57</t>
+          <t>07/01 14:50:11</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,17 +305,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>33734.94</t>
+          <t>46987.95</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>向文</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>06/30 13:00:19</t>
+          <t>06/30 13:54:57</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,12 +347,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>38554.22</t>
+          <t>33734.94</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>李志伟</t>
+          <t>马瑞昭</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>06/30 10:47:16</t>
+          <t>06/30 13:00:19</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,12 +389,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>33734.94</t>
+          <t>38554.22</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>耿振云</t>
+          <t>李志伟</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>06/30 10:22:52</t>
+          <t>06/30 10:47:16</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,17 +426,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>114634.15</t>
+          <t>33734.94</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t/>
+          <t>耿振云</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>06/30 10:08:02</t>
+          <t>06/30 10:22:52</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,17 +468,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>114634.15</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06/29 12:46:37</t>
+          <t>06/30 10:08:02</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -515,12 +515,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>林伟超</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06/27 13:03:05</t>
+          <t>06/29 12:46:37</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,17 +552,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>6172.84</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t/>
+          <t>林伟超</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06/27 11:42:49</t>
+          <t>06/27 13:03:05</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>6172.84</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06/26 14:40:59</t>
+          <t>06/27 11:42:49</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06/25 16:34:17</t>
+          <t>06/26 14:40:59</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,17 +678,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>48192.77</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06/24 12:36:33</t>
+          <t>06/25 16:34:17</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>21428.57</t>
+          <t>48192.77</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -747,166 +747,181 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>06/24 12:36:33</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>180000</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>21428.57</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>马瑞昭</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>06/24 12:08:55</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>24096.39</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>羊美云</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/02 19:00:39</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>128241</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/02 12:32:59</t>
+          <t>07/02 19:00:39</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>128241</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -928,12 +943,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/01 16:52:50</t>
+          <t>07/02 12:32:59</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>77108</t>
+          <t>27710</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -955,12 +970,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06/30 15:16:34</t>
+          <t>07/01 16:52:50</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>72289</t>
+          <t>77108</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -982,12 +997,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06/30 12:16:11</t>
+          <t>06/30 15:16:34</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>68610</t>
+          <t>72289</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -997,7 +1012,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1009,12 +1024,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06/30 11:50:16</t>
+          <t>06/30 12:16:11</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>61000</t>
+          <t>68610</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1024,7 +1039,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1036,12 +1051,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06/30 11:35:36</t>
+          <t>06/30 11:50:16</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>79000</t>
+          <t>61000</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1063,12 +1078,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06/29 14:04:21</t>
+          <t>06/30 11:35:36</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>79000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1090,12 +1105,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06/27 13:07:43</t>
+          <t>06/29 14:04:21</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>42317</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1105,7 +1120,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1117,12 +1132,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06/26 16:07:20</t>
+          <t>06/27 13:07:43</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>42317</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1132,7 +1147,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1144,12 +1159,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06/25 19:22:04</t>
+          <t>06/26 16:07:20</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>48192</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1171,83 +1186,110 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>06/25 19:22:04</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>48192</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>06/24 14:10:57</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>45524</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="40"/>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="41"/>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>5684390</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>685985.74</t>
+          <t>5684378</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>685991</t>
+          <t>685973.74</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>685991</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>-5.26</t>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>-17.26</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/03 20:29:29</t>
+          <t>07/04 15:50:29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,39 +90,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>20238.1</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t>向超</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>moucai1111</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/02 15:47:40</t>
+          <t>07/03 20:29:29</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1064400</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,39 +132,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>128240.96</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t>上海浦东新区 明天上午11</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>moucai1111</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t/>
+          <t>17万 问</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/02 09:17:34</t>
+          <t>07/02 15:47:40</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>1064400</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,17 +179,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>27710.84</t>
+          <t>128240.96</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>王志宽</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/01 18:40:00</t>
+          <t>07/02 09:17:34</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,22 +216,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>27710.84</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 安徽 明天 9.00</t>
+          <t>王志宽</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>nn40007</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/01 15:40:01</t>
+          <t>07/01 18:40:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,22 +258,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>林伟超</t>
+          <t>:安徽省阜阳市临泉县杨桥镇 安徽 明天 9.00</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>nn40007</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/01 14:50:11</t>
+          <t>07/01 15:40:01</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,17 +305,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>46987.95</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>向文</t>
+          <t>林伟超</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>06/30 13:54:57</t>
+          <t>07/01 14:50:11</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,17 +347,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>33734.94</t>
+          <t>46987.95</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>向文</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>06/30 13:00:19</t>
+          <t>06/30 13:54:57</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,12 +389,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>38554.22</t>
+          <t>33734.94</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>李志伟</t>
+          <t>马瑞昭</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>06/30 10:47:16</t>
+          <t>06/30 13:00:19</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -431,12 +431,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>33734.94</t>
+          <t>38554.22</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>耿振云</t>
+          <t>李志伟</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>06/30 10:22:52</t>
+          <t>06/30 10:47:16</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,17 +468,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>114634.15</t>
+          <t>33734.94</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t/>
+          <t>耿振云</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06/30 10:08:02</t>
+          <t>06/30 10:22:52</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,17 +510,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>114634.15</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06/29 12:46:37</t>
+          <t>06/30 10:08:02</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -557,12 +557,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>林伟超</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06/27 13:03:05</t>
+          <t>06/29 12:46:37</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,17 +594,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>6172.84</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t/>
+          <t>林伟超</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06/27 11:42:49</t>
+          <t>06/27 13:03:05</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>6172.84</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06/26 14:40:59</t>
+          <t>06/27 11:42:49</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06/25 16:34:17</t>
+          <t>06/26 14:40:59</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>48192.77</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06/24 12:36:33</t>
+          <t>06/25 16:34:17</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,17 +762,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>21428.57</t>
+          <t>48192.77</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -789,166 +789,181 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>06/24 12:36:33</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>180000</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>21428.57</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>马瑞昭</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>06/24 12:08:55</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>24096.39</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>羊美云</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/02 19:00:39</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>128241</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/02 12:32:59</t>
+          <t>07/02 19:00:39</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>128241</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -970,12 +985,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/01 16:52:50</t>
+          <t>07/02 12:32:59</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>77108</t>
+          <t>27710</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -997,12 +1012,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06/30 15:16:34</t>
+          <t>07/01 16:52:50</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>72289</t>
+          <t>77108</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1024,12 +1039,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06/30 12:16:11</t>
+          <t>06/30 15:16:34</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>68610</t>
+          <t>72289</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1039,7 +1054,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1051,12 +1066,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06/30 11:50:16</t>
+          <t>06/30 12:16:11</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>61000</t>
+          <t>68610</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1066,7 +1081,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1078,12 +1093,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06/30 11:35:36</t>
+          <t>06/30 11:50:16</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>79000</t>
+          <t>61000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1105,12 +1120,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06/29 14:04:21</t>
+          <t>06/30 11:35:36</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>79000</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1132,12 +1147,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06/27 13:07:43</t>
+          <t>06/29 14:04:21</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>42317</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1147,7 +1162,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1159,12 +1174,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06/26 16:07:20</t>
+          <t>06/27 13:07:43</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>42317</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1174,7 +1189,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1186,12 +1201,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06/25 19:22:04</t>
+          <t>06/26 16:07:20</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>48192</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1213,83 +1228,110 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>06/25 19:22:04</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>48192</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>06/24 14:10:57</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>45524</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="41"/>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>5684378</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>685973.74</t>
+          <t>5854378</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>685991</t>
+          <t>706211.84</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>685991</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>-17.26</t>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>20220.84</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
@@ -958,12 +958,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/02 19:00:39</t>
+          <t>07/04 17:10:11</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>128241</t>
+          <t>20238</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -985,12 +985,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/02 12:32:59</t>
+          <t>07/02 19:00:39</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>128241</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1012,12 +1012,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/01 16:52:50</t>
+          <t>07/02 12:32:59</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>77108</t>
+          <t>27710</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1039,12 +1039,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06/30 15:16:34</t>
+          <t>07/01 16:52:50</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>72289</t>
+          <t>77108</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1066,12 +1066,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06/30 12:16:11</t>
+          <t>06/30 15:16:34</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>68610</t>
+          <t>72289</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1093,12 +1093,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06/30 11:50:16</t>
+          <t>06/30 12:16:11</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>61000</t>
+          <t>68610</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1120,12 +1120,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06/30 11:35:36</t>
+          <t>06/30 11:50:16</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>79000</t>
+          <t>61000</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1147,12 +1147,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06/29 14:04:21</t>
+          <t>06/30 11:35:36</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>79000</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1174,12 +1174,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06/27 13:07:43</t>
+          <t>06/29 14:04:21</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>42317</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1201,12 +1201,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06/26 16:07:20</t>
+          <t>06/27 13:07:43</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>42317</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1228,12 +1228,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06/25 19:22:04</t>
+          <t>06/26 16:07:20</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>48192</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1255,83 +1255,110 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>06/25 19:22:04</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>48192</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>06/24 14:10:57</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>45524</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="42"/>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="43"/>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>5854378</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>706211.84</t>
+          <t>5854378</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>685991</t>
+          <t>706211.84</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>706229</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>20220.84</t>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>-17.16</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/04 15:50:29</t>
+          <t>07/06 16:38:03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,12 +95,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>20238.1</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>向超</t>
+          <t>孔令智</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/03 20:29:29</t>
+          <t>07/04 15:50:29</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,39 +132,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>20238.1</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t>向超</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>moucai1111</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/02 15:47:40</t>
+          <t>07/03 20:29:29</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1064400</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,39 +174,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>128240.96</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t>上海浦东新区 明天上午11</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>moucai1111</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t/>
+          <t>17万 问</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/02 09:17:34</t>
+          <t>07/02 15:47:40</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>1064400</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,17 +221,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>27710.84</t>
+          <t>128240.96</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>王志宽</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/01 18:40:00</t>
+          <t>07/02 09:17:34</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,22 +258,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>27710.84</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 安徽 明天 9.00</t>
+          <t>王志宽</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>nn40007</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/01 15:40:01</t>
+          <t>07/01 18:40:00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,22 +300,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>林伟超</t>
+          <t>:安徽省阜阳市临泉县杨桥镇 安徽 明天 9.00</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>nn40007</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/01 14:50:11</t>
+          <t>07/01 15:40:01</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,17 +347,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>46987.95</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>向文</t>
+          <t>林伟超</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>06/30 13:54:57</t>
+          <t>07/01 14:50:11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,17 +389,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>33734.94</t>
+          <t>46987.95</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>向文</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>06/30 13:00:19</t>
+          <t>06/30 13:54:57</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -431,12 +431,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>38554.22</t>
+          <t>33734.94</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>李志伟</t>
+          <t>马瑞昭</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>06/30 10:47:16</t>
+          <t>06/30 13:00:19</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -473,12 +473,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>33734.94</t>
+          <t>38554.22</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>耿振云</t>
+          <t>李志伟</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06/30 10:22:52</t>
+          <t>06/30 10:47:16</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,17 +510,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>114634.15</t>
+          <t>33734.94</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t/>
+          <t>耿振云</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06/30 10:08:02</t>
+          <t>06/30 10:22:52</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,17 +552,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>114634.15</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06/29 12:46:37</t>
+          <t>06/30 10:08:02</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -599,12 +599,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>林伟超</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06/27 13:03:05</t>
+          <t>06/29 12:46:37</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,17 +636,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>6172.84</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t/>
+          <t>林伟超</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06/27 11:42:49</t>
+          <t>06/27 13:03:05</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>6172.84</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06/26 14:40:59</t>
+          <t>06/27 11:42:49</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06/25 16:34:17</t>
+          <t>06/26 14:40:59</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,17 +762,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>48192.77</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06/24 12:36:33</t>
+          <t>06/25 16:34:17</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,17 +804,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>21428.57</t>
+          <t>48192.77</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -831,166 +831,181 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>06/24 12:36:33</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>180000</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>21428.57</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>马瑞昭</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>06/24 12:08:55</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>24096.39</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>羊美云</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/04 17:10:11</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>20238</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/02 19:00:39</t>
+          <t>07/04 17:10:11</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>128241</t>
+          <t>20238</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1012,12 +1027,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/02 12:32:59</t>
+          <t>07/02 19:00:39</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>128241</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1039,12 +1054,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/01 16:52:50</t>
+          <t>07/02 12:32:59</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>77108</t>
+          <t>27710</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1066,12 +1081,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06/30 15:16:34</t>
+          <t>07/01 16:52:50</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>72289</t>
+          <t>77108</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1093,12 +1108,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06/30 12:16:11</t>
+          <t>06/30 15:16:34</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>68610</t>
+          <t>72289</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1108,7 +1123,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1120,12 +1135,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06/30 11:50:16</t>
+          <t>06/30 12:16:11</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>61000</t>
+          <t>68610</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1135,7 +1150,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1147,12 +1162,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06/30 11:35:36</t>
+          <t>06/30 11:50:16</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>79000</t>
+          <t>61000</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1174,12 +1189,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06/29 14:04:21</t>
+          <t>06/30 11:35:36</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>79000</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1201,12 +1216,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06/27 13:07:43</t>
+          <t>06/29 14:04:21</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>42317</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1216,7 +1231,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1228,12 +1243,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06/26 16:07:20</t>
+          <t>06/27 13:07:43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>42317</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1243,7 +1258,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1255,12 +1270,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06/25 19:22:04</t>
+          <t>06/26 16:07:20</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>48192</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1282,83 +1297,110 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>06/25 19:22:04</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>48192</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>06/24 14:10:57</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>45524</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="43"/>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="44"/>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>5854378</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>706211.84</t>
+          <t>5954378</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>706229</t>
+          <t>718116.6</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>706229</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>-17.16</t>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>11887.6</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
@@ -1000,12 +1000,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/04 17:10:11</t>
+          <t>07/06 17:52:23</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>20238</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1027,12 +1027,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/02 19:00:39</t>
+          <t>07/04 17:10:11</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>128241</t>
+          <t>20238</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1054,12 +1054,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/02 12:32:59</t>
+          <t>07/02 19:00:39</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>128241</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1081,12 +1081,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/01 16:52:50</t>
+          <t>07/02 12:32:59</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>77108</t>
+          <t>27710</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1108,12 +1108,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06/30 15:16:34</t>
+          <t>07/01 16:52:50</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>72289</t>
+          <t>77108</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1135,12 +1135,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06/30 12:16:11</t>
+          <t>06/30 15:16:34</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>68610</t>
+          <t>72289</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1162,12 +1162,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06/30 11:50:16</t>
+          <t>06/30 12:16:11</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>61000</t>
+          <t>68610</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1189,12 +1189,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06/30 11:35:36</t>
+          <t>06/30 11:50:16</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>79000</t>
+          <t>61000</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1216,12 +1216,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06/29 14:04:21</t>
+          <t>06/30 11:35:36</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>79000</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1243,12 +1243,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06/27 13:07:43</t>
+          <t>06/29 14:04:21</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>42317</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1270,12 +1270,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06/26 16:07:20</t>
+          <t>06/27 13:07:43</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>42317</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1297,12 +1297,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06/25 19:22:04</t>
+          <t>06/26 16:07:20</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>48192</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1324,83 +1324,110 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>06/25 19:22:04</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>48192</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>06/24 14:10:57</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>45524</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="44"/>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="45"/>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>5954378</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>718116.6</t>
+          <t>5954378</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>706229</t>
+          <t>718116.6</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>718133</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>11887.6</t>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>-16.4</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
@@ -75,7 +75,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/06 16:38:03</t>
+          <t>07/09 09:53:40</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -100,12 +100,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>孔令智</t>
+          <t/>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/04 15:50:29</t>
+          <t>07/06 16:38:03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,12 +137,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>20238.1</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>向超</t>
+          <t>孔令智</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/03 20:29:29</t>
+          <t>07/04 15:50:29</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,39 +174,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>20238.1</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t>向超</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>moucai1111</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/02 15:47:40</t>
+          <t>07/03 20:29:29</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1064400</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,39 +216,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>128240.96</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t>上海浦东新区 明天上午11</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>moucai1111</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t/>
+          <t>17万 问</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/02 09:17:34</t>
+          <t>07/02 15:47:40</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>1064400</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,17 +263,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>27710.84</t>
+          <t>128240.96</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>王志宽</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/01 18:40:00</t>
+          <t>07/02 09:17:34</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,22 +300,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>27710.84</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 安徽 明天 9.00</t>
+          <t>王志宽</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>nn40007</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/01 15:40:01</t>
+          <t>07/01 18:40:00</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,22 +342,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>林伟超</t>
+          <t>:安徽省阜阳市临泉县杨桥镇 安徽 明天 9.00</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>nn40007</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/01 14:50:11</t>
+          <t>07/01 15:40:01</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,17 +389,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>46987.95</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>向文</t>
+          <t>林伟超</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>06/30 13:54:57</t>
+          <t>07/01 14:50:11</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -431,17 +431,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>33734.94</t>
+          <t>46987.95</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>向文</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>06/30 13:00:19</t>
+          <t>06/30 13:54:57</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -473,12 +473,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>38554.22</t>
+          <t>33734.94</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>李志伟</t>
+          <t>马瑞昭</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06/30 10:47:16</t>
+          <t>06/30 13:00:19</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -515,12 +515,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>33734.94</t>
+          <t>38554.22</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>耿振云</t>
+          <t>李志伟</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06/30 10:22:52</t>
+          <t>06/30 10:47:16</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,17 +552,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>114634.15</t>
+          <t>33734.94</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t/>
+          <t>耿振云</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06/30 10:08:02</t>
+          <t>06/30 10:22:52</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,17 +594,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>114634.15</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06/29 12:46:37</t>
+          <t>06/30 10:08:02</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -641,12 +641,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>林伟超</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06/27 13:03:05</t>
+          <t>06/29 12:46:37</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,17 +678,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>6172.84</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t/>
+          <t>林伟超</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06/27 11:42:49</t>
+          <t>06/27 13:03:05</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>6172.84</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06/26 14:40:59</t>
+          <t>06/27 11:42:49</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06/25 16:34:17</t>
+          <t>06/26 14:40:59</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,17 +804,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>48192.77</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06/24 12:36:33</t>
+          <t>06/25 16:34:17</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,17 +846,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>21428.57</t>
+          <t>48192.77</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -873,166 +873,181 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>06/24 12:36:33</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>180000</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>21428.57</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>马瑞昭</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>06/24 12:08:55</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>24096.39</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>羊美云</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/06 17:52:23</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/04 17:10:11</t>
+          <t>07/06 17:52:23</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20238</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1054,12 +1069,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/02 19:00:39</t>
+          <t>07/04 17:10:11</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>128241</t>
+          <t>20238</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1081,12 +1096,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/02 12:32:59</t>
+          <t>07/02 19:00:39</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>128241</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1108,12 +1123,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/01 16:52:50</t>
+          <t>07/02 12:32:59</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>77108</t>
+          <t>27710</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1135,12 +1150,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06/30 15:16:34</t>
+          <t>07/01 16:52:50</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>72289</t>
+          <t>77108</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1162,12 +1177,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06/30 12:16:11</t>
+          <t>06/30 15:16:34</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>68610</t>
+          <t>72289</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1177,7 +1192,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1189,12 +1204,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06/30 11:50:16</t>
+          <t>06/30 12:16:11</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>61000</t>
+          <t>68610</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1204,7 +1219,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1216,12 +1231,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06/30 11:35:36</t>
+          <t>06/30 11:50:16</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>79000</t>
+          <t>61000</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1243,12 +1258,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06/29 14:04:21</t>
+          <t>06/30 11:35:36</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>79000</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1270,12 +1285,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06/27 13:07:43</t>
+          <t>06/29 14:04:21</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>42317</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1285,7 +1300,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1297,12 +1312,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06/26 16:07:20</t>
+          <t>06/27 13:07:43</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>42317</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1312,7 +1327,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1324,12 +1339,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06/25 19:22:04</t>
+          <t>06/26 16:07:20</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>48192</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1351,83 +1366,110 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>06/25 19:22:04</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>48192</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>06/24 14:10:57</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>45524</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="45"/>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="46"/>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>5954378</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>718116.6</t>
+          <t>6054378</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>718133</t>
+          <t>730021.36</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>718133</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>-16.4</t>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>11888.36</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/09 09:53:40</t>
+          <t>07/09 09:54:13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,17 +90,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>44578.31</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t/>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -117,7 +117,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/06 16:38:03</t>
+          <t>07/09 09:53:40</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -142,12 +142,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>孔令智</t>
+          <t/>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/04 15:50:29</t>
+          <t>07/06 16:38:03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,12 +179,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>20238.1</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>向超</t>
+          <t>孔令智</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/03 20:29:29</t>
+          <t>07/04 15:50:29</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,39 +216,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>20238.1</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t>向超</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>moucai1111</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/02 15:47:40</t>
+          <t>07/03 20:29:29</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1064400</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,39 +258,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>128240.96</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t>上海浦东新区 明天上午11</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>moucai1111</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t/>
+          <t>17万 问</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/02 09:17:34</t>
+          <t>07/02 15:47:40</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>1064400</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,17 +305,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>27710.84</t>
+          <t>128240.96</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>王志宽</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/01 18:40:00</t>
+          <t>07/02 09:17:34</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,22 +342,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>27710.84</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 安徽 明天 9.00</t>
+          <t>王志宽</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>nn40007</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/01 15:40:01</t>
+          <t>07/01 18:40:00</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,22 +384,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>林伟超</t>
+          <t>:安徽省阜阳市临泉县杨桥镇 安徽 明天 9.00</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>nn40007</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/01 14:50:11</t>
+          <t>07/01 15:40:01</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -431,17 +431,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>46987.95</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>向文</t>
+          <t>林伟超</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>06/30 13:54:57</t>
+          <t>07/01 14:50:11</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -473,17 +473,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>33734.94</t>
+          <t>46987.95</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>向文</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06/30 13:00:19</t>
+          <t>06/30 13:54:57</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -515,12 +515,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>38554.22</t>
+          <t>33734.94</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>李志伟</t>
+          <t>马瑞昭</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06/30 10:47:16</t>
+          <t>06/30 13:00:19</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -557,12 +557,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>33734.94</t>
+          <t>38554.22</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>耿振云</t>
+          <t>李志伟</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06/30 10:22:52</t>
+          <t>06/30 10:47:16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,17 +594,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>114634.15</t>
+          <t>33734.94</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t/>
+          <t>耿振云</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06/30 10:08:02</t>
+          <t>06/30 10:22:52</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,17 +636,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>114634.15</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06/29 12:46:37</t>
+          <t>06/30 10:08:02</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -683,12 +683,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>林伟超</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06/27 13:03:05</t>
+          <t>06/29 12:46:37</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>6172.84</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t/>
+          <t>林伟超</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06/27 11:42:49</t>
+          <t>06/27 13:03:05</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>6172.84</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06/26 14:40:59</t>
+          <t>06/27 11:42:49</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06/25 16:34:17</t>
+          <t>06/26 14:40:59</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,17 +846,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>48192.77</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06/24 12:36:33</t>
+          <t>06/25 16:34:17</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,17 +888,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>21428.57</t>
+          <t>48192.77</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -915,166 +915,181 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>06/24 12:36:33</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>180000</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>21428.57</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>马瑞昭</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>06/24 12:08:55</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>24096.39</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>羊美云</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/06 17:52:23</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/04 17:10:11</t>
+          <t>07/06 17:52:23</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>20238</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1096,12 +1111,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/02 19:00:39</t>
+          <t>07/04 17:10:11</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>128241</t>
+          <t>20238</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1123,12 +1138,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/02 12:32:59</t>
+          <t>07/02 19:00:39</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>128241</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1150,12 +1165,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/01 16:52:50</t>
+          <t>07/02 12:32:59</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>77108</t>
+          <t>27710</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1177,12 +1192,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06/30 15:16:34</t>
+          <t>07/01 16:52:50</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>72289</t>
+          <t>77108</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1204,12 +1219,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06/30 12:16:11</t>
+          <t>06/30 15:16:34</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>68610</t>
+          <t>72289</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1219,7 +1234,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1231,12 +1246,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06/30 11:50:16</t>
+          <t>06/30 12:16:11</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>61000</t>
+          <t>68610</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1246,7 +1261,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1258,12 +1273,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06/30 11:35:36</t>
+          <t>06/30 11:50:16</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>79000</t>
+          <t>61000</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1285,12 +1300,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06/29 14:04:21</t>
+          <t>06/30 11:35:36</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>79000</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1312,12 +1327,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06/27 13:07:43</t>
+          <t>06/29 14:04:21</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>42317</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1327,7 +1342,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1339,12 +1354,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06/26 16:07:20</t>
+          <t>06/27 13:07:43</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>42317</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1354,7 +1369,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1366,12 +1381,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06/25 19:22:04</t>
+          <t>06/26 16:07:20</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>48192</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1393,83 +1408,110 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>06/25 19:22:04</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>48192</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t>06/24 14:10:57</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>45524</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="46"/>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="47"/>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>6054378</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>730021.36</t>
+          <t>6424378</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>718133</t>
+          <t>774599.67</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>718133</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>11888.36</t>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>56466.67</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
@@ -13,7 +13,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>群组：金鑫供大牛全国取现</t>
+          <t>群组：金鑫供大牛全国取现DD</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -1084,12 +1084,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/06 17:52:23</t>
+          <t>07/09 11:40:53</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>56483</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1111,12 +1111,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/04 17:10:11</t>
+          <t>07/06 17:52:23</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>20238</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1138,12 +1138,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/02 19:00:39</t>
+          <t>07/04 17:10:11</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>128241</t>
+          <t>20238</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1165,12 +1165,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/02 12:32:59</t>
+          <t>07/02 19:00:39</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>128241</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1192,12 +1192,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/01 16:52:50</t>
+          <t>07/02 12:32:59</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>77108</t>
+          <t>27710</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1219,12 +1219,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06/30 15:16:34</t>
+          <t>07/01 16:52:50</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>72289</t>
+          <t>77108</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1246,12 +1246,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06/30 12:16:11</t>
+          <t>06/30 15:16:34</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>68610</t>
+          <t>72289</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1273,12 +1273,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06/30 11:50:16</t>
+          <t>06/30 12:16:11</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>61000</t>
+          <t>68610</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1300,12 +1300,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06/30 11:35:36</t>
+          <t>06/30 11:50:16</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>79000</t>
+          <t>61000</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1327,12 +1327,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06/29 14:04:21</t>
+          <t>06/30 11:35:36</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>79000</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1354,12 +1354,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06/27 13:07:43</t>
+          <t>06/29 14:04:21</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>42317</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1381,12 +1381,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06/26 16:07:20</t>
+          <t>06/27 13:07:43</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>42317</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1408,12 +1408,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06/25 19:22:04</t>
+          <t>06/26 16:07:20</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>48192</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1435,83 +1435,110 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>06/25 19:22:04</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>48192</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>06/24 14:10:57</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>45524</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="47"/>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="48"/>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>6424378</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>774599.67</t>
+          <t>6424378</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>718133</t>
+          <t>774599.67</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>774616</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>56466.67</t>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>-16.33</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/09 09:54:13</t>
+          <t>07/10 13:45:23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,17 +90,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>44578.31</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t>向文</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/09 09:53:40</t>
+          <t>07/09 09:54:13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,17 +132,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>44578.31</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t/>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -159,7 +159,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/06 16:38:03</t>
+          <t>07/09 09:53:40</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -184,12 +184,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>孔令智</t>
+          <t/>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/04 15:50:29</t>
+          <t>07/06 16:38:03</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,12 +221,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>20238.1</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>向超</t>
+          <t>孔令智</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/03 20:29:29</t>
+          <t>07/04 15:50:29</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,39 +258,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>20238.1</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t>向超</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>moucai1111</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/02 15:47:40</t>
+          <t>07/03 20:29:29</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1064400</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,39 +300,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>128240.96</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t>上海浦东新区 明天上午11</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>moucai1111</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t/>
+          <t>17万 问</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/02 09:17:34</t>
+          <t>07/02 15:47:40</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>1064400</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,17 +347,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>27710.84</t>
+          <t>128240.96</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>王志宽</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/01 18:40:00</t>
+          <t>07/02 09:17:34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,22 +384,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>27710.84</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 安徽 明天 9.00</t>
+          <t>王志宽</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>nn40007</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/01 15:40:01</t>
+          <t>07/01 18:40:00</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,22 +426,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>林伟超</t>
+          <t>:安徽省阜阳市临泉县杨桥镇 安徽 明天 9.00</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>nn40007</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/01 14:50:11</t>
+          <t>07/01 15:40:01</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -473,17 +473,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>46987.95</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>向文</t>
+          <t>林伟超</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06/30 13:54:57</t>
+          <t>07/01 14:50:11</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -515,17 +515,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>33734.94</t>
+          <t>46987.95</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>向文</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06/30 13:00:19</t>
+          <t>06/30 13:54:57</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -557,12 +557,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>38554.22</t>
+          <t>33734.94</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>李志伟</t>
+          <t>马瑞昭</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06/30 10:47:16</t>
+          <t>06/30 13:00:19</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -599,12 +599,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>33734.94</t>
+          <t>38554.22</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>耿振云</t>
+          <t>李志伟</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06/30 10:22:52</t>
+          <t>06/30 10:47:16</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,17 +636,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>114634.15</t>
+          <t>33734.94</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t/>
+          <t>耿振云</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06/30 10:08:02</t>
+          <t>06/30 10:22:52</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,17 +678,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>114634.15</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06/29 12:46:37</t>
+          <t>06/30 10:08:02</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -725,12 +725,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>林伟超</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06/27 13:03:05</t>
+          <t>06/29 12:46:37</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,17 +762,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>6172.84</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t/>
+          <t>林伟超</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06/27 11:42:49</t>
+          <t>06/27 13:03:05</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>6172.84</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06/26 14:40:59</t>
+          <t>06/27 11:42:49</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06/25 16:34:17</t>
+          <t>06/26 14:40:59</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,17 +888,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>48192.77</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06/24 12:36:33</t>
+          <t>06/25 16:34:17</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,17 +930,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>21428.57</t>
+          <t>48192.77</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -957,166 +957,181 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>06/24 12:36:33</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>180000</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>21428.57</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>马瑞昭</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>06/24 12:08:55</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>24096.39</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>羊美云</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/09 11:40:53</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>56483</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/06 17:52:23</t>
+          <t>07/09 11:40:53</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>56483</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1138,12 +1153,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/04 17:10:11</t>
+          <t>07/06 17:52:23</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>20238</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1165,12 +1180,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/02 19:00:39</t>
+          <t>07/04 17:10:11</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>128241</t>
+          <t>20238</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1192,12 +1207,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/02 12:32:59</t>
+          <t>07/02 19:00:39</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>128241</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1219,12 +1234,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/01 16:52:50</t>
+          <t>07/02 12:32:59</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>77108</t>
+          <t>27710</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1246,12 +1261,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06/30 15:16:34</t>
+          <t>07/01 16:52:50</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>72289</t>
+          <t>77108</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1273,12 +1288,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06/30 12:16:11</t>
+          <t>06/30 15:16:34</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>68610</t>
+          <t>72289</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1288,7 +1303,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1300,12 +1315,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06/30 11:50:16</t>
+          <t>06/30 12:16:11</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>61000</t>
+          <t>68610</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1315,7 +1330,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1327,12 +1342,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06/30 11:35:36</t>
+          <t>06/30 11:50:16</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>79000</t>
+          <t>61000</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1354,12 +1369,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06/29 14:04:21</t>
+          <t>06/30 11:35:36</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>79000</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1381,12 +1396,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06/27 13:07:43</t>
+          <t>06/29 14:04:21</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>42317</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1396,7 +1411,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1408,12 +1423,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06/26 16:07:20</t>
+          <t>06/27 13:07:43</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>42317</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1423,7 +1438,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1435,12 +1450,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06/25 19:22:04</t>
+          <t>06/26 16:07:20</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>48192</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1462,83 +1477,110 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>06/25 19:22:04</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>48192</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>06/24 14:10:57</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>45524</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="48"/>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="49"/>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>6424378</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>774599.67</t>
+          <t>6524378</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>774616</t>
+          <t>786504.44</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>774616</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>-16.33</t>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>11888.44</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/10 13:45:23</t>
+          <t>07/10 14:56:17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,17 +90,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>向文</t>
+          <t/>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/09 09:54:13</t>
+          <t>07/10 13:45:23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,17 +132,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>44578.31</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t>向文</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/09 09:53:40</t>
+          <t>07/09 09:54:13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,17 +174,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>44578.31</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t/>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -201,7 +201,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/06 16:38:03</t>
+          <t>07/09 09:53:40</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -226,12 +226,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>孔令智</t>
+          <t/>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/04 15:50:29</t>
+          <t>07/06 16:38:03</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,12 +263,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>20238.1</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>向超</t>
+          <t>孔令智</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/03 20:29:29</t>
+          <t>07/04 15:50:29</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,39 +300,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>20238.1</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t>向超</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>moucai1111</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/02 15:47:40</t>
+          <t>07/03 20:29:29</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1064400</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,39 +342,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>128240.96</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t>上海浦东新区 明天上午11</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>moucai1111</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t/>
+          <t>17万 问</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/02 09:17:34</t>
+          <t>07/02 15:47:40</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>1064400</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,17 +389,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>27710.84</t>
+          <t>128240.96</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>王志宽</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/01 18:40:00</t>
+          <t>07/02 09:17:34</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,22 +426,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>27710.84</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 安徽 明天 9.00</t>
+          <t>王志宽</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>nn40007</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/01 15:40:01</t>
+          <t>07/01 18:40:00</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,22 +468,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>林伟超</t>
+          <t>:安徽省阜阳市临泉县杨桥镇 安徽 明天 9.00</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>nn40007</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/01 14:50:11</t>
+          <t>07/01 15:40:01</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -515,17 +515,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>46987.95</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>向文</t>
+          <t>林伟超</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06/30 13:54:57</t>
+          <t>07/01 14:50:11</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -557,17 +557,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>33734.94</t>
+          <t>46987.95</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>向文</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06/30 13:00:19</t>
+          <t>06/30 13:54:57</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -599,12 +599,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>38554.22</t>
+          <t>33734.94</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>李志伟</t>
+          <t>马瑞昭</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06/30 10:47:16</t>
+          <t>06/30 13:00:19</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -641,12 +641,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>33734.94</t>
+          <t>38554.22</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>耿振云</t>
+          <t>李志伟</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06/30 10:22:52</t>
+          <t>06/30 10:47:16</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,17 +678,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>114634.15</t>
+          <t>33734.94</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t/>
+          <t>耿振云</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06/30 10:08:02</t>
+          <t>06/30 10:22:52</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>114634.15</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06/29 12:46:37</t>
+          <t>06/30 10:08:02</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>林伟超</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06/27 13:03:05</t>
+          <t>06/29 12:46:37</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,17 +804,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>6172.84</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t/>
+          <t>林伟超</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06/27 11:42:49</t>
+          <t>06/27 13:03:05</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>6172.84</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06/26 14:40:59</t>
+          <t>06/27 11:42:49</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06/25 16:34:17</t>
+          <t>06/26 14:40:59</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,17 +930,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>48192.77</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06/24 12:36:33</t>
+          <t>06/25 16:34:17</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,17 +972,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>21428.57</t>
+          <t>48192.77</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -999,166 +999,181 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>06/24 12:36:33</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>180000</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>21428.57</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>马瑞昭</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>06/24 12:08:55</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>24096.39</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>羊美云</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/09 11:40:53</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>56483</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/06 17:52:23</t>
+          <t>07/09 11:40:53</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>56483</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1180,12 +1195,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/04 17:10:11</t>
+          <t>07/06 17:52:23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>20238</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1207,12 +1222,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/02 19:00:39</t>
+          <t>07/04 17:10:11</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>128241</t>
+          <t>20238</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1234,12 +1249,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/02 12:32:59</t>
+          <t>07/02 19:00:39</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>128241</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1261,12 +1276,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/01 16:52:50</t>
+          <t>07/02 12:32:59</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>77108</t>
+          <t>27710</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1288,12 +1303,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06/30 15:16:34</t>
+          <t>07/01 16:52:50</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>72289</t>
+          <t>77108</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1315,12 +1330,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06/30 12:16:11</t>
+          <t>06/30 15:16:34</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>68610</t>
+          <t>72289</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1330,7 +1345,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1342,12 +1357,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06/30 11:50:16</t>
+          <t>06/30 12:16:11</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>61000</t>
+          <t>68610</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1357,7 +1372,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1369,12 +1384,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06/30 11:35:36</t>
+          <t>06/30 11:50:16</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>79000</t>
+          <t>61000</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1396,12 +1411,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06/29 14:04:21</t>
+          <t>06/30 11:35:36</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>79000</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1423,12 +1438,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06/27 13:07:43</t>
+          <t>06/29 14:04:21</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>42317</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1438,7 +1453,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1450,12 +1465,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06/26 16:07:20</t>
+          <t>06/27 13:07:43</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>42317</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1465,7 +1480,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1477,12 +1492,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06/25 19:22:04</t>
+          <t>06/26 16:07:20</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>48192</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1504,83 +1519,110 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>06/25 19:22:04</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>48192</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
           <t>06/24 14:10:57</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>45524</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
+      <c r="C49" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="49"/>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="50"/>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>6524378</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>786504.44</t>
+          <t>6824378</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>774616</t>
+          <t>822649.01</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>774616</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>11888.44</t>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>48033.01</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
@@ -1168,12 +1168,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/09 11:40:53</t>
+          <t>07/10 18:27:46</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>56483</t>
+          <t>48049</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1195,12 +1195,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/06 17:52:23</t>
+          <t>07/09 11:40:53</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>56483</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1222,12 +1222,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/04 17:10:11</t>
+          <t>07/06 17:52:23</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>20238</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1249,12 +1249,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/02 19:00:39</t>
+          <t>07/04 17:10:11</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>128241</t>
+          <t>20238</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1276,12 +1276,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/02 12:32:59</t>
+          <t>07/02 19:00:39</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>128241</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1303,12 +1303,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/01 16:52:50</t>
+          <t>07/02 12:32:59</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>77108</t>
+          <t>27710</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1330,12 +1330,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06/30 15:16:34</t>
+          <t>07/01 16:52:50</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>72289</t>
+          <t>77108</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1357,12 +1357,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06/30 12:16:11</t>
+          <t>06/30 15:16:34</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>68610</t>
+          <t>72289</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1384,12 +1384,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06/30 11:50:16</t>
+          <t>06/30 12:16:11</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>61000</t>
+          <t>68610</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1411,12 +1411,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06/30 11:35:36</t>
+          <t>06/30 11:50:16</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>79000</t>
+          <t>61000</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1438,12 +1438,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06/29 14:04:21</t>
+          <t>06/30 11:35:36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>79000</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1465,12 +1465,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06/27 13:07:43</t>
+          <t>06/29 14:04:21</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>42317</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1492,12 +1492,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06/26 16:07:20</t>
+          <t>06/27 13:07:43</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>42317</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1519,12 +1519,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06/25 19:22:04</t>
+          <t>06/26 16:07:20</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>48192</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1546,83 +1546,110 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>06/25 19:22:04</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>48192</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t>06/24 14:10:57</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>45524</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="50"/>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="51"/>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>6824378</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>822649.01</t>
+          <t>6824378</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>774616</t>
+          <t>822649.01</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>822665</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>48033.01</t>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>-15.99</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/10 14:56:17</t>
+          <t>07/12 18:24:59</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>7407.41</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/10 13:45:23</t>
+          <t>07/10 14:56:17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,17 +132,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>向文</t>
+          <t/>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/09 09:54:13</t>
+          <t>07/10 13:45:23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,17 +174,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>44578.31</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t>向文</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/09 09:53:40</t>
+          <t>07/09 09:54:13</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,17 +216,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>44578.31</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t/>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -243,7 +243,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/06 16:38:03</t>
+          <t>07/09 09:53:40</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -268,12 +268,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>孔令智</t>
+          <t/>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/04 15:50:29</t>
+          <t>07/06 16:38:03</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,12 +305,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>20238.1</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>向超</t>
+          <t>孔令智</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/03 20:29:29</t>
+          <t>07/04 15:50:29</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,39 +342,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>20238.1</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t>向超</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>moucai1111</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/02 15:47:40</t>
+          <t>07/03 20:29:29</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1064400</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,39 +384,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>128240.96</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t>上海浦东新区 明天上午11</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>moucai1111</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t/>
+          <t>17万 问</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/02 09:17:34</t>
+          <t>07/02 15:47:40</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>1064400</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -431,17 +431,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>27710.84</t>
+          <t>128240.96</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>王志宽</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/01 18:40:00</t>
+          <t>07/02 09:17:34</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,22 +468,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>27710.84</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 安徽 明天 9.00</t>
+          <t>王志宽</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>nn40007</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/01 15:40:01</t>
+          <t>07/01 18:40:00</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,22 +510,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>林伟超</t>
+          <t>:安徽省阜阳市临泉县杨桥镇 安徽 明天 9.00</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>nn40007</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/01 14:50:11</t>
+          <t>07/01 15:40:01</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -557,17 +557,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>46987.95</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>向文</t>
+          <t>林伟超</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06/30 13:54:57</t>
+          <t>07/01 14:50:11</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -599,17 +599,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>33734.94</t>
+          <t>46987.95</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>向文</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06/30 13:00:19</t>
+          <t>06/30 13:54:57</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -641,12 +641,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>38554.22</t>
+          <t>33734.94</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>李志伟</t>
+          <t>马瑞昭</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06/30 10:47:16</t>
+          <t>06/30 13:00:19</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -683,12 +683,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>33734.94</t>
+          <t>38554.22</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>耿振云</t>
+          <t>李志伟</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06/30 10:22:52</t>
+          <t>06/30 10:47:16</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>114634.15</t>
+          <t>33734.94</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t/>
+          <t>耿振云</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06/30 10:08:02</t>
+          <t>06/30 10:22:52</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,17 +762,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>114634.15</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06/29 12:46:37</t>
+          <t>06/30 10:08:02</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -809,12 +809,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>林伟超</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06/27 13:03:05</t>
+          <t>06/29 12:46:37</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,17 +846,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>6172.84</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t/>
+          <t>林伟超</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06/27 11:42:49</t>
+          <t>06/27 13:03:05</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>6172.84</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06/26 14:40:59</t>
+          <t>06/27 11:42:49</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06/25 16:34:17</t>
+          <t>06/26 14:40:59</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,17 +972,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>48192.77</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06/24 12:36:33</t>
+          <t>06/25 16:34:17</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,17 +1014,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>21428.57</t>
+          <t>48192.77</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1041,166 +1041,181 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>06/24 12:36:33</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>180000</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>21428.57</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>马瑞昭</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>06/24 12:08:55</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>24096.39</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>羊美云</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/10 18:27:46</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>48049</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/09 11:40:53</t>
+          <t>07/10 18:27:46</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>56483</t>
+          <t>48049</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1222,12 +1237,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/06 17:52:23</t>
+          <t>07/09 11:40:53</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>56483</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1249,12 +1264,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/04 17:10:11</t>
+          <t>07/06 17:52:23</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>20238</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1276,12 +1291,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/02 19:00:39</t>
+          <t>07/04 17:10:11</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>128241</t>
+          <t>20238</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1303,12 +1318,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/02 12:32:59</t>
+          <t>07/02 19:00:39</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>128241</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1330,12 +1345,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/01 16:52:50</t>
+          <t>07/02 12:32:59</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>77108</t>
+          <t>27710</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1357,12 +1372,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06/30 15:16:34</t>
+          <t>07/01 16:52:50</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>72289</t>
+          <t>77108</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1384,12 +1399,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06/30 12:16:11</t>
+          <t>06/30 15:16:34</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>68610</t>
+          <t>72289</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1399,7 +1414,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1411,12 +1426,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06/30 11:50:16</t>
+          <t>06/30 12:16:11</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>61000</t>
+          <t>68610</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1426,7 +1441,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1438,12 +1453,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06/30 11:35:36</t>
+          <t>06/30 11:50:16</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>79000</t>
+          <t>61000</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1465,12 +1480,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06/29 14:04:21</t>
+          <t>06/30 11:35:36</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>79000</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1492,12 +1507,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06/27 13:07:43</t>
+          <t>06/29 14:04:21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>42317</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1507,7 +1522,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1519,12 +1534,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06/26 16:07:20</t>
+          <t>06/27 13:07:43</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>42317</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1534,7 +1549,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1546,12 +1561,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06/25 19:22:04</t>
+          <t>06/26 16:07:20</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>48192</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1573,83 +1588,110 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>06/25 19:22:04</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>48192</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
           <t>06/24 14:10:57</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>45524</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="51"/>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="52"/>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>6824378</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>822649.01</t>
+          <t>6884378</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>822665</t>
+          <t>830056.42</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>822665</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>-15.99</t>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>7391.42</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
@@ -1210,12 +1210,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/10 18:27:46</t>
+          <t>07/12 18:26:46</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>48049</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1237,12 +1237,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/09 11:40:53</t>
+          <t>07/10 18:27:46</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>56483</t>
+          <t>48049</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1264,12 +1264,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/06 17:52:23</t>
+          <t>07/09 11:40:53</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>56483</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1291,12 +1291,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/04 17:10:11</t>
+          <t>07/06 17:52:23</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>20238</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1318,12 +1318,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/02 19:00:39</t>
+          <t>07/04 17:10:11</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>128241</t>
+          <t>20238</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1345,12 +1345,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/02 12:32:59</t>
+          <t>07/02 19:00:39</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>128241</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1372,12 +1372,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/01 16:52:50</t>
+          <t>07/02 12:32:59</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>77108</t>
+          <t>27710</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1399,12 +1399,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06/30 15:16:34</t>
+          <t>07/01 16:52:50</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>72289</t>
+          <t>77108</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1426,12 +1426,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06/30 12:16:11</t>
+          <t>06/30 15:16:34</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>68610</t>
+          <t>72289</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1453,12 +1453,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06/30 11:50:16</t>
+          <t>06/30 12:16:11</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>61000</t>
+          <t>68610</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1480,12 +1480,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06/30 11:35:36</t>
+          <t>06/30 11:50:16</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>79000</t>
+          <t>61000</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1507,12 +1507,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06/29 14:04:21</t>
+          <t>06/30 11:35:36</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>79000</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1534,12 +1534,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06/27 13:07:43</t>
+          <t>06/29 14:04:21</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>42317</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1561,12 +1561,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06/26 16:07:20</t>
+          <t>06/27 13:07:43</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>42317</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1588,12 +1588,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06/25 19:22:04</t>
+          <t>06/26 16:07:20</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>48192</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1615,83 +1615,110 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>06/25 19:22:04</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>48192</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t>06/24 14:10:57</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>45524</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
+      <c r="C52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="52"/>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="53"/>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>6884378</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>830056.42</t>
+          <t>6884378</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>822665</t>
+          <t>830056.42</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>823665</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>7391.42</t>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>6391.42</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
@@ -1210,12 +1210,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/12 18:26:46</t>
+          <t>07/12 18:39:01</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>6407</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1237,12 +1237,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/10 18:27:46</t>
+          <t>07/12 18:26:46</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>48049</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1264,12 +1264,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/09 11:40:53</t>
+          <t>07/10 18:27:46</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>56483</t>
+          <t>48049</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1291,12 +1291,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/06 17:52:23</t>
+          <t>07/09 11:40:53</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>56483</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1318,12 +1318,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/04 17:10:11</t>
+          <t>07/06 17:52:23</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>20238</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1345,12 +1345,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/02 19:00:39</t>
+          <t>07/04 17:10:11</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>128241</t>
+          <t>20238</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1372,12 +1372,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/02 12:32:59</t>
+          <t>07/02 19:00:39</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>128241</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1399,12 +1399,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/01 16:52:50</t>
+          <t>07/02 12:32:59</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>77108</t>
+          <t>27710</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1426,12 +1426,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06/30 15:16:34</t>
+          <t>07/01 16:52:50</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>72289</t>
+          <t>77108</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1453,12 +1453,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06/30 12:16:11</t>
+          <t>06/30 15:16:34</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>68610</t>
+          <t>72289</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1480,12 +1480,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06/30 11:50:16</t>
+          <t>06/30 12:16:11</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>61000</t>
+          <t>68610</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1507,12 +1507,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06/30 11:35:36</t>
+          <t>06/30 11:50:16</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>79000</t>
+          <t>61000</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1534,12 +1534,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06/29 14:04:21</t>
+          <t>06/30 11:35:36</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>79000</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1561,12 +1561,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06/27 13:07:43</t>
+          <t>06/29 14:04:21</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>42317</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1588,12 +1588,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06/26 16:07:20</t>
+          <t>06/27 13:07:43</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>42317</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1615,12 +1615,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06/25 19:22:04</t>
+          <t>06/26 16:07:20</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>48192</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1642,83 +1642,110 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>06/25 19:22:04</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>48192</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
           <t>06/24 14:10:57</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>45524</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
+      <c r="C53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="53"/>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="54"/>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>6884378</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>830056.42</t>
+          <t>6884378</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>823665</t>
+          <t>830056.42</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>830072</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>6391.42</t>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>-15.58</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/12 18:24:59</t>
+          <t>07/14 19:36:37</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,17 +90,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>7407.41</t>
+          <t>27710.84</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t/>
+          <t>马瑞昭</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/10 14:56:17</t>
+          <t>07/12 18:24:59</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>7407.41</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/10 13:45:23</t>
+          <t>07/10 14:56:17</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,17 +174,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>向文</t>
+          <t/>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/09 09:54:13</t>
+          <t>07/10 13:45:23</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,17 +216,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>44578.31</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t>向文</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/09 09:53:40</t>
+          <t>07/09 09:54:13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,17 +258,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>44578.31</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t/>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -285,7 +285,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/06 16:38:03</t>
+          <t>07/09 09:53:40</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -310,12 +310,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>孔令智</t>
+          <t/>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/04 15:50:29</t>
+          <t>07/06 16:38:03</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,12 +347,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>20238.1</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>向超</t>
+          <t>孔令智</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/03 20:29:29</t>
+          <t>07/04 15:50:29</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,39 +384,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>20238.1</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t>向超</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>moucai1111</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/02 15:47:40</t>
+          <t>07/03 20:29:29</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1064400</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,39 +426,39 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>128240.96</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t>上海浦东新区 明天上午11</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>moucai1111</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t/>
+          <t>17万 问</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/02 09:17:34</t>
+          <t>07/02 15:47:40</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>1064400</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -473,17 +473,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>27710.84</t>
+          <t>128240.96</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>王志宽</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/01 18:40:00</t>
+          <t>07/02 09:17:34</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,22 +510,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>27710.84</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 安徽 明天 9.00</t>
+          <t>王志宽</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>nn40007</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/01 15:40:01</t>
+          <t>07/01 18:40:00</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,22 +552,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>林伟超</t>
+          <t>:安徽省阜阳市临泉县杨桥镇 安徽 明天 9.00</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>nn40007</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/01 14:50:11</t>
+          <t>07/01 15:40:01</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -599,17 +599,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>46987.95</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>向文</t>
+          <t>林伟超</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06/30 13:54:57</t>
+          <t>07/01 14:50:11</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -641,17 +641,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>33734.94</t>
+          <t>46987.95</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>向文</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06/30 13:00:19</t>
+          <t>06/30 13:54:57</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -683,12 +683,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>38554.22</t>
+          <t>33734.94</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>李志伟</t>
+          <t>马瑞昭</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06/30 10:47:16</t>
+          <t>06/30 13:00:19</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -725,12 +725,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>33734.94</t>
+          <t>38554.22</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>耿振云</t>
+          <t>李志伟</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06/30 10:22:52</t>
+          <t>06/30 10:47:16</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,17 +762,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>114634.15</t>
+          <t>33734.94</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t/>
+          <t>耿振云</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06/30 10:08:02</t>
+          <t>06/30 10:22:52</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,17 +804,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>114634.15</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06/29 12:46:37</t>
+          <t>06/30 10:08:02</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -851,12 +851,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>林伟超</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06/27 13:03:05</t>
+          <t>06/29 12:46:37</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,17 +888,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>6172.84</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t/>
+          <t>林伟超</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06/27 11:42:49</t>
+          <t>06/27 13:03:05</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>6172.84</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06/26 14:40:59</t>
+          <t>06/27 11:42:49</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06/25 16:34:17</t>
+          <t>06/26 14:40:59</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,17 +1014,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>48192.77</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06/24 12:36:33</t>
+          <t>06/25 16:34:17</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,17 +1056,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>21428.57</t>
+          <t>48192.77</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1083,166 +1083,181 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>06/24 12:36:33</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>180000</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>21428.57</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>马瑞昭</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>06/24 12:08:55</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>24096.39</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>羊美云</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="33"/>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/12 18:39:01</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>6407</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/12 18:26:46</t>
+          <t>07/12 18:39:01</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>6407</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1264,12 +1279,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/10 18:27:46</t>
+          <t>07/12 18:26:46</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>48049</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1279,7 +1294,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1291,12 +1306,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/09 11:40:53</t>
+          <t>07/10 18:27:46</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>56483</t>
+          <t>48049</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1318,12 +1333,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/06 17:52:23</t>
+          <t>07/09 11:40:53</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>56483</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1345,12 +1360,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/04 17:10:11</t>
+          <t>07/06 17:52:23</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>20238</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1372,12 +1387,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/02 19:00:39</t>
+          <t>07/04 17:10:11</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>128241</t>
+          <t>20238</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1399,12 +1414,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/02 12:32:59</t>
+          <t>07/02 19:00:39</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>128241</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1426,12 +1441,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/01 16:52:50</t>
+          <t>07/02 12:32:59</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>77108</t>
+          <t>27710</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1453,12 +1468,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06/30 15:16:34</t>
+          <t>07/01 16:52:50</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>72289</t>
+          <t>77108</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1480,12 +1495,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06/30 12:16:11</t>
+          <t>06/30 15:16:34</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>68610</t>
+          <t>72289</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1495,7 +1510,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1507,12 +1522,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06/30 11:50:16</t>
+          <t>06/30 12:16:11</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>61000</t>
+          <t>68610</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1522,7 +1537,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1534,12 +1549,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06/30 11:35:36</t>
+          <t>06/30 11:50:16</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>79000</t>
+          <t>61000</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1561,12 +1576,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06/29 14:04:21</t>
+          <t>06/30 11:35:36</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>79000</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1588,12 +1603,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06/27 13:07:43</t>
+          <t>06/29 14:04:21</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>42317</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1603,7 +1618,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1615,12 +1630,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06/26 16:07:20</t>
+          <t>06/27 13:07:43</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>42317</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1630,7 +1645,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1642,12 +1657,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06/25 19:22:04</t>
+          <t>06/26 16:07:20</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>48192</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1669,83 +1684,110 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>06/25 19:22:04</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>48192</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
           <t>06/24 14:10:57</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>45524</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
+      <c r="C54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="54"/>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="55"/>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>6884378</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>830056.42</t>
+          <t>7114378</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>830072</t>
+          <t>857767.26</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>830072</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>-15.58</t>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>27695.26</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
@@ -1252,12 +1252,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/12 18:39:01</t>
+          <t>07/14 20:52:08</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>6407</t>
+          <t>27710</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1279,12 +1279,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/12 18:26:46</t>
+          <t>07/12 18:39:01</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>6407</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1306,12 +1306,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/10 18:27:46</t>
+          <t>07/12 18:26:46</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>48049</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1333,12 +1333,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/09 11:40:53</t>
+          <t>07/10 18:27:46</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>56483</t>
+          <t>48049</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1360,12 +1360,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/06 17:52:23</t>
+          <t>07/09 11:40:53</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>56483</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1387,12 +1387,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/04 17:10:11</t>
+          <t>07/06 17:52:23</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>20238</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1414,12 +1414,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/02 19:00:39</t>
+          <t>07/04 17:10:11</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>128241</t>
+          <t>20238</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1441,12 +1441,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/02 12:32:59</t>
+          <t>07/02 19:00:39</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>128241</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1468,12 +1468,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/01 16:52:50</t>
+          <t>07/02 12:32:59</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>77108</t>
+          <t>27710</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1495,12 +1495,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06/30 15:16:34</t>
+          <t>07/01 16:52:50</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>72289</t>
+          <t>77108</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1522,12 +1522,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06/30 12:16:11</t>
+          <t>06/30 15:16:34</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>68610</t>
+          <t>72289</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1549,12 +1549,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06/30 11:50:16</t>
+          <t>06/30 12:16:11</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>61000</t>
+          <t>68610</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1576,12 +1576,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06/30 11:35:36</t>
+          <t>06/30 11:50:16</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>79000</t>
+          <t>61000</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1603,12 +1603,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06/29 14:04:21</t>
+          <t>06/30 11:35:36</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>79000</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1630,12 +1630,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06/27 13:07:43</t>
+          <t>06/29 14:04:21</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>42317</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1657,12 +1657,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06/26 16:07:20</t>
+          <t>06/27 13:07:43</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>42317</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1684,12 +1684,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06/25 19:22:04</t>
+          <t>06/26 16:07:20</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>48192</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1711,83 +1711,110 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>06/25 19:22:04</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>48192</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
           <t>06/24 14:10:57</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>45524</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
+      <c r="C55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="55"/>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="56"/>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>7114378</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>857767.26</t>
+          <t>7114378</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>830072</t>
+          <t>857767.26</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>857782</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>27695.26</t>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>-14.74</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/14 19:36:37</t>
+          <t>07/17 17:11:15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,12 +95,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>27710.84</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/12 18:24:59</t>
+          <t>07/14 19:36:37</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,17 +132,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>7407.41</t>
+          <t>27710.84</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t/>
+          <t>马瑞昭</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/10 14:56:17</t>
+          <t>07/12 18:24:59</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>7407.41</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/10 13:45:23</t>
+          <t>07/10 14:56:17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,17 +216,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>向文</t>
+          <t/>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/09 09:54:13</t>
+          <t>07/10 13:45:23</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,17 +258,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>44578.31</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t>向文</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/09 09:53:40</t>
+          <t>07/09 09:54:13</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,17 +300,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>44578.31</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t/>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -327,7 +327,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/06 16:38:03</t>
+          <t>07/09 09:53:40</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -352,12 +352,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>孔令智</t>
+          <t/>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/04 15:50:29</t>
+          <t>07/06 16:38:03</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,12 +389,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>20238.1</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>向超</t>
+          <t>孔令智</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/03 20:29:29</t>
+          <t>07/04 15:50:29</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,39 +426,39 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>20238.1</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t>向超</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>moucai1111</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/02 15:47:40</t>
+          <t>07/03 20:29:29</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1064400</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,39 +468,39 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>128240.96</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t>上海浦东新区 明天上午11</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>moucai1111</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t/>
+          <t>17万 问</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/02 09:17:34</t>
+          <t>07/02 15:47:40</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>1064400</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -515,17 +515,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>27710.84</t>
+          <t>128240.96</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>王志宽</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/01 18:40:00</t>
+          <t>07/02 09:17:34</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,22 +552,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>27710.84</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 安徽 明天 9.00</t>
+          <t>王志宽</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>nn40007</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/01 15:40:01</t>
+          <t>07/01 18:40:00</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,22 +594,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>林伟超</t>
+          <t>:安徽省阜阳市临泉县杨桥镇 安徽 明天 9.00</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>nn40007</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/01 14:50:11</t>
+          <t>07/01 15:40:01</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -641,17 +641,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>46987.95</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>向文</t>
+          <t>林伟超</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06/30 13:54:57</t>
+          <t>07/01 14:50:11</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -683,17 +683,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>33734.94</t>
+          <t>46987.95</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>向文</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06/30 13:00:19</t>
+          <t>06/30 13:54:57</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -725,12 +725,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>38554.22</t>
+          <t>33734.94</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>李志伟</t>
+          <t>马瑞昭</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06/30 10:47:16</t>
+          <t>06/30 13:00:19</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>33734.94</t>
+          <t>38554.22</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>耿振云</t>
+          <t>李志伟</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06/30 10:22:52</t>
+          <t>06/30 10:47:16</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,17 +804,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>114634.15</t>
+          <t>33734.94</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t/>
+          <t>耿振云</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06/30 10:08:02</t>
+          <t>06/30 10:22:52</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,17 +846,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>114634.15</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06/29 12:46:37</t>
+          <t>06/30 10:08:02</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>林伟超</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06/27 13:03:05</t>
+          <t>06/29 12:46:37</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,17 +930,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>6172.84</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t/>
+          <t>林伟超</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06/27 11:42:49</t>
+          <t>06/27 13:03:05</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>6172.84</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06/26 14:40:59</t>
+          <t>06/27 11:42:49</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06/25 16:34:17</t>
+          <t>06/26 14:40:59</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,17 +1056,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>48192.77</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06/24 12:36:33</t>
+          <t>06/25 16:34:17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,17 +1098,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>21428.57</t>
+          <t>48192.77</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1125,166 +1125,181 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>06/24 12:36:33</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>180000</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>21428.57</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>马瑞昭</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>06/24 12:08:55</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>24096.39</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>羊美云</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="34"/>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/14 20:52:08</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/12 18:39:01</t>
+          <t>07/14 20:52:08</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>6407</t>
+          <t>27710</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1306,12 +1321,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/12 18:26:46</t>
+          <t>07/12 18:39:01</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>6407</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1333,12 +1348,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/10 18:27:46</t>
+          <t>07/12 18:26:46</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>48049</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1348,7 +1363,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1360,12 +1375,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/09 11:40:53</t>
+          <t>07/10 18:27:46</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>56483</t>
+          <t>48049</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1387,12 +1402,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/06 17:52:23</t>
+          <t>07/09 11:40:53</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>56483</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1414,12 +1429,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/04 17:10:11</t>
+          <t>07/06 17:52:23</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>20238</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1441,12 +1456,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/02 19:00:39</t>
+          <t>07/04 17:10:11</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>128241</t>
+          <t>20238</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1468,12 +1483,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/02 12:32:59</t>
+          <t>07/02 19:00:39</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>128241</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1495,12 +1510,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07/01 16:52:50</t>
+          <t>07/02 12:32:59</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>77108</t>
+          <t>27710</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1522,12 +1537,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06/30 15:16:34</t>
+          <t>07/01 16:52:50</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>72289</t>
+          <t>77108</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1549,12 +1564,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06/30 12:16:11</t>
+          <t>06/30 15:16:34</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>68610</t>
+          <t>72289</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1564,7 +1579,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1576,12 +1591,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06/30 11:50:16</t>
+          <t>06/30 12:16:11</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>61000</t>
+          <t>68610</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1591,7 +1606,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1603,12 +1618,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06/30 11:35:36</t>
+          <t>06/30 11:50:16</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>79000</t>
+          <t>61000</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1630,12 +1645,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06/29 14:04:21</t>
+          <t>06/30 11:35:36</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>79000</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1657,12 +1672,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06/27 13:07:43</t>
+          <t>06/29 14:04:21</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>42317</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1672,7 +1687,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1684,12 +1699,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06/26 16:07:20</t>
+          <t>06/27 13:07:43</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>42317</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1699,7 +1714,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1711,12 +1726,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06/25 19:22:04</t>
+          <t>06/26 16:07:20</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>48192</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1738,83 +1753,110 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>06/25 19:22:04</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>48192</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>06/24 14:10:57</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>45524</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
+      <c r="C56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="56"/>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="57"/>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>7114378</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>857767.26</t>
+          <t>7364378</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>857782</t>
+          <t>887887.75</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>857782</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>-14.74</t>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>30105.75</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/17 17:11:15</t>
+          <t>07/17 18:15:22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>183843</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,22 +90,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>21886.07</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/14 19:36:37</t>
+          <t>07/17 17:11:15</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,12 +137,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>27710.84</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/12 18:24:59</t>
+          <t>07/14 19:36:37</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,17 +174,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>7407.41</t>
+          <t>27710.84</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t/>
+          <t>马瑞昭</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/10 14:56:17</t>
+          <t>07/12 18:24:59</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>7407.41</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/10 13:45:23</t>
+          <t>07/10 14:56:17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,17 +258,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>向文</t>
+          <t/>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/09 09:54:13</t>
+          <t>07/10 13:45:23</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,17 +300,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>44578.31</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t>向文</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/09 09:53:40</t>
+          <t>07/09 09:54:13</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,17 +342,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>44578.31</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t/>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -369,7 +369,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/06 16:38:03</t>
+          <t>07/09 09:53:40</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -394,12 +394,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>孔令智</t>
+          <t/>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/04 15:50:29</t>
+          <t>07/06 16:38:03</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -431,12 +431,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>20238.1</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>向超</t>
+          <t>孔令智</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/03 20:29:29</t>
+          <t>07/04 15:50:29</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,39 +468,39 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>20238.1</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t>向超</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>moucai1111</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/02 15:47:40</t>
+          <t>07/03 20:29:29</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1064400</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,39 +510,39 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>128240.96</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t>上海浦东新区 明天上午11</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>moucai1111</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t/>
+          <t>17万 问</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/02 09:17:34</t>
+          <t>07/02 15:47:40</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>1064400</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -557,17 +557,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>27710.84</t>
+          <t>128240.96</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>王志宽</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/01 18:40:00</t>
+          <t>07/02 09:17:34</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,22 +594,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>27710.84</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 安徽 明天 9.00</t>
+          <t>王志宽</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>nn40007</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/01 15:40:01</t>
+          <t>07/01 18:40:00</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,22 +636,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>林伟超</t>
+          <t>:安徽省阜阳市临泉县杨桥镇 安徽 明天 9.00</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>nn40007</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/01 14:50:11</t>
+          <t>07/01 15:40:01</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -683,17 +683,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>46987.95</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>向文</t>
+          <t>林伟超</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06/30 13:54:57</t>
+          <t>07/01 14:50:11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -725,17 +725,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>33734.94</t>
+          <t>46987.95</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>向文</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06/30 13:00:19</t>
+          <t>06/30 13:54:57</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>38554.22</t>
+          <t>33734.94</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>李志伟</t>
+          <t>马瑞昭</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06/30 10:47:16</t>
+          <t>06/30 13:00:19</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -809,12 +809,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>33734.94</t>
+          <t>38554.22</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>耿振云</t>
+          <t>李志伟</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06/30 10:22:52</t>
+          <t>06/30 10:47:16</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,17 +846,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>114634.15</t>
+          <t>33734.94</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t/>
+          <t>耿振云</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06/30 10:08:02</t>
+          <t>06/30 10:22:52</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,17 +888,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>114634.15</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06/29 12:46:37</t>
+          <t>06/30 10:08:02</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -935,12 +935,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>林伟超</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06/27 13:03:05</t>
+          <t>06/29 12:46:37</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,17 +972,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>6172.84</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t/>
+          <t>林伟超</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06/27 11:42:49</t>
+          <t>06/27 13:03:05</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>6172.84</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06/26 14:40:59</t>
+          <t>06/27 11:42:49</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06/25 16:34:17</t>
+          <t>06/26 14:40:59</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,17 +1098,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>48192.77</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06/24 12:36:33</t>
+          <t>06/25 16:34:17</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,17 +1140,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>21428.57</t>
+          <t>48192.77</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1167,166 +1167,181 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>06/24 12:36:33</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>180000</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>21428.57</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>马瑞昭</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>06/24 12:08:55</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>24096.39</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>羊美云</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="36"/>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/14 20:52:08</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/12 18:39:01</t>
+          <t>07/14 20:52:08</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>6407</t>
+          <t>27710</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1348,12 +1363,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/12 18:26:46</t>
+          <t>07/12 18:39:01</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>6407</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1375,12 +1390,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/10 18:27:46</t>
+          <t>07/12 18:26:46</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>48049</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1390,7 +1405,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1402,12 +1417,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/09 11:40:53</t>
+          <t>07/10 18:27:46</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>56483</t>
+          <t>48049</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1429,12 +1444,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/06 17:52:23</t>
+          <t>07/09 11:40:53</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>56483</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1456,12 +1471,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/04 17:10:11</t>
+          <t>07/06 17:52:23</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>20238</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1483,12 +1498,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/02 19:00:39</t>
+          <t>07/04 17:10:11</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>128241</t>
+          <t>20238</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1510,12 +1525,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07/02 12:32:59</t>
+          <t>07/02 19:00:39</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>128241</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1537,12 +1552,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07/01 16:52:50</t>
+          <t>07/02 12:32:59</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>77108</t>
+          <t>27710</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1564,12 +1579,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06/30 15:16:34</t>
+          <t>07/01 16:52:50</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>72289</t>
+          <t>77108</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1591,12 +1606,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06/30 12:16:11</t>
+          <t>06/30 15:16:34</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>68610</t>
+          <t>72289</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1606,7 +1621,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1618,12 +1633,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06/30 11:50:16</t>
+          <t>06/30 12:16:11</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>61000</t>
+          <t>68610</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1633,7 +1648,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1645,12 +1660,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06/30 11:35:36</t>
+          <t>06/30 11:50:16</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>79000</t>
+          <t>61000</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1672,12 +1687,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06/29 14:04:21</t>
+          <t>06/30 11:35:36</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>79000</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1699,12 +1714,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06/27 13:07:43</t>
+          <t>06/29 14:04:21</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>42317</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1714,7 +1729,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1726,12 +1741,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06/26 16:07:20</t>
+          <t>06/27 13:07:43</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>42317</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1741,7 +1756,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -1753,12 +1768,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06/25 19:22:04</t>
+          <t>06/26 16:07:20</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>48192</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1780,83 +1795,110 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>06/25 19:22:04</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>48192</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
           <t>06/24 14:10:57</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>45524</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
+      <c r="C57" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="57"/>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="58"/>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>7364378</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>887887.75</t>
+          <t>7548221</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>857782</t>
+          <t>909773.82</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>857782</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>30105.75</t>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>51991.82</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
@@ -1336,12 +1336,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/14 20:52:08</t>
+          <t>07/17 19:45:53</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>52006</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1363,12 +1363,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/12 18:39:01</t>
+          <t>07/14 20:52:08</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>6407</t>
+          <t>27710</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1390,12 +1390,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/12 18:26:46</t>
+          <t>07/12 18:39:01</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>6407</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1417,12 +1417,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/10 18:27:46</t>
+          <t>07/12 18:26:46</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>48049</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1444,12 +1444,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/09 11:40:53</t>
+          <t>07/10 18:27:46</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>56483</t>
+          <t>48049</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1471,12 +1471,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/06 17:52:23</t>
+          <t>07/09 11:40:53</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>56483</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1498,12 +1498,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/04 17:10:11</t>
+          <t>07/06 17:52:23</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>20238</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1525,12 +1525,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07/02 19:00:39</t>
+          <t>07/04 17:10:11</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>128241</t>
+          <t>20238</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1552,12 +1552,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07/02 12:32:59</t>
+          <t>07/02 19:00:39</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>128241</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1579,12 +1579,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07/01 16:52:50</t>
+          <t>07/02 12:32:59</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>77108</t>
+          <t>27710</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1606,12 +1606,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06/30 15:16:34</t>
+          <t>07/01 16:52:50</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>72289</t>
+          <t>77108</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1633,12 +1633,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06/30 12:16:11</t>
+          <t>06/30 15:16:34</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>68610</t>
+          <t>72289</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1660,12 +1660,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06/30 11:50:16</t>
+          <t>06/30 12:16:11</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>61000</t>
+          <t>68610</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1687,12 +1687,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06/30 11:35:36</t>
+          <t>06/30 11:50:16</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>79000</t>
+          <t>61000</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1714,12 +1714,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06/29 14:04:21</t>
+          <t>06/30 11:35:36</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>79000</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1741,12 +1741,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06/27 13:07:43</t>
+          <t>06/29 14:04:21</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>42317</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -1768,12 +1768,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06/26 16:07:20</t>
+          <t>06/27 13:07:43</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>42317</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -1795,12 +1795,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06/25 19:22:04</t>
+          <t>06/26 16:07:20</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>48192</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1822,83 +1822,110 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>06/25 19:22:04</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>48192</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
           <t>06/24 14:10:57</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>45524</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
+      <c r="C58" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="58"/>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="59"/>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>7548221</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>909773.82</t>
+          <t>7548221</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>857782</t>
+          <t>909773.82</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>909788</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>51991.82</t>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>-14.18</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/17 18:15:22</t>
+          <t>07/18 15:08:49</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>183843</t>
+          <t>87400</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,22 +90,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>21886.07</t>
+          <t>10790.12</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t/>
+          <t>马瑞昭</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/17 17:11:15</t>
+          <t>07/17 18:15:22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>183843</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,22 +132,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>21886.07</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/14 19:36:37</t>
+          <t>07/17 17:11:15</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,12 +179,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>27710.84</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/12 18:24:59</t>
+          <t>07/14 19:36:37</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,17 +216,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>7407.41</t>
+          <t>27710.84</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t/>
+          <t>马瑞昭</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/10 14:56:17</t>
+          <t>07/12 18:24:59</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>7407.41</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/10 13:45:23</t>
+          <t>07/10 14:56:17</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,17 +300,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>向文</t>
+          <t/>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/09 09:54:13</t>
+          <t>07/10 13:45:23</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,17 +342,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>44578.31</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t>向文</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/09 09:53:40</t>
+          <t>07/09 09:54:13</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,17 +384,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>44578.31</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t/>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -411,7 +411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/06 16:38:03</t>
+          <t>07/09 09:53:40</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -436,12 +436,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>孔令智</t>
+          <t/>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/04 15:50:29</t>
+          <t>07/06 16:38:03</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -473,12 +473,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>20238.1</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>向超</t>
+          <t>孔令智</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/03 20:29:29</t>
+          <t>07/04 15:50:29</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,39 +510,39 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>20238.1</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t>向超</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>moucai1111</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/02 15:47:40</t>
+          <t>07/03 20:29:29</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1064400</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,39 +552,39 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>128240.96</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t>上海浦东新区 明天上午11</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>moucai1111</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t/>
+          <t>17万 问</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/02 09:17:34</t>
+          <t>07/02 15:47:40</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>1064400</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -599,17 +599,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>27710.84</t>
+          <t>128240.96</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>王志宽</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/01 18:40:00</t>
+          <t>07/02 09:17:34</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,22 +636,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>27710.84</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 安徽 明天 9.00</t>
+          <t>王志宽</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>nn40007</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/01 15:40:01</t>
+          <t>07/01 18:40:00</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,22 +678,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>林伟超</t>
+          <t>:安徽省阜阳市临泉县杨桥镇 安徽 明天 9.00</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>nn40007</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/01 14:50:11</t>
+          <t>07/01 15:40:01</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -725,17 +725,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>46987.95</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>向文</t>
+          <t>林伟超</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06/30 13:54:57</t>
+          <t>07/01 14:50:11</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -767,17 +767,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>33734.94</t>
+          <t>46987.95</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>向文</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06/30 13:00:19</t>
+          <t>06/30 13:54:57</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -809,12 +809,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>38554.22</t>
+          <t>33734.94</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>李志伟</t>
+          <t>马瑞昭</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06/30 10:47:16</t>
+          <t>06/30 13:00:19</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -851,12 +851,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>33734.94</t>
+          <t>38554.22</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>耿振云</t>
+          <t>李志伟</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06/30 10:22:52</t>
+          <t>06/30 10:47:16</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,17 +888,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>114634.15</t>
+          <t>33734.94</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t/>
+          <t>耿振云</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06/30 10:08:02</t>
+          <t>06/30 10:22:52</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,17 +930,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>114634.15</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06/29 12:46:37</t>
+          <t>06/30 10:08:02</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -977,12 +977,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>林伟超</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06/27 13:03:05</t>
+          <t>06/29 12:46:37</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,17 +1014,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>6172.84</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t/>
+          <t>林伟超</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06/27 11:42:49</t>
+          <t>06/27 13:03:05</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>6172.84</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06/26 14:40:59</t>
+          <t>06/27 11:42:49</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06/25 16:34:17</t>
+          <t>06/26 14:40:59</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,17 +1140,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>48192.77</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06/24 12:36:33</t>
+          <t>06/25 16:34:17</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1182,17 +1182,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>21428.57</t>
+          <t>48192.77</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1209,166 +1209,181 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>06/24 12:36:33</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>180000</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>21428.57</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>马瑞昭</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>06/24 12:08:55</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>24096.39</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>羊美云</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="33"/>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="36"/>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/17 19:45:53</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>52006</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/14 20:52:08</t>
+          <t>07/17 19:45:53</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>52006</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1378,7 +1393,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1390,12 +1405,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/12 18:39:01</t>
+          <t>07/14 20:52:08</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>6407</t>
+          <t>27710</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1417,12 +1432,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/12 18:26:46</t>
+          <t>07/12 18:39:01</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>6407</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1444,12 +1459,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/10 18:27:46</t>
+          <t>07/12 18:26:46</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>48049</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1459,7 +1474,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1471,12 +1486,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/09 11:40:53</t>
+          <t>07/10 18:27:46</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>56483</t>
+          <t>48049</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1498,12 +1513,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/06 17:52:23</t>
+          <t>07/09 11:40:53</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>56483</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1525,12 +1540,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07/04 17:10:11</t>
+          <t>07/06 17:52:23</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>20238</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1552,12 +1567,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07/02 19:00:39</t>
+          <t>07/04 17:10:11</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>128241</t>
+          <t>20238</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1579,12 +1594,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07/02 12:32:59</t>
+          <t>07/02 19:00:39</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>128241</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1606,12 +1621,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07/01 16:52:50</t>
+          <t>07/02 12:32:59</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>77108</t>
+          <t>27710</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1633,12 +1648,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06/30 15:16:34</t>
+          <t>07/01 16:52:50</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>72289</t>
+          <t>77108</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1660,12 +1675,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06/30 12:16:11</t>
+          <t>06/30 15:16:34</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>68610</t>
+          <t>72289</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1675,7 +1690,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1687,12 +1702,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06/30 11:50:16</t>
+          <t>06/30 12:16:11</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>61000</t>
+          <t>68610</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1702,7 +1717,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1714,12 +1729,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06/30 11:35:36</t>
+          <t>06/30 11:50:16</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>79000</t>
+          <t>61000</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1741,12 +1756,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06/29 14:04:21</t>
+          <t>06/30 11:35:36</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>79000</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1768,12 +1783,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06/27 13:07:43</t>
+          <t>06/29 14:04:21</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>42317</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1783,7 +1798,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -1795,12 +1810,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06/26 16:07:20</t>
+          <t>06/27 13:07:43</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>42317</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1810,7 +1825,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -1822,12 +1837,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06/25 19:22:04</t>
+          <t>06/26 16:07:20</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>48192</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1849,83 +1864,110 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>06/25 19:22:04</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>48192</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
           <t>06/24 14:10:57</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>45524</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
+      <c r="C59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="59"/>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="60"/>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>7548221</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>909773.82</t>
+          <t>7635621</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>909788</t>
+          <t>920563.94</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>909788</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>-14.18</t>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>10775.94</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
@@ -1378,12 +1378,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/17 19:45:53</t>
+          <t>07/18 17:18:15</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>52006</t>
+          <t>10790</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1405,12 +1405,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/14 20:52:08</t>
+          <t>07/17 19:45:53</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>52006</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1432,12 +1432,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/12 18:39:01</t>
+          <t>07/14 20:52:08</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>6407</t>
+          <t>27710</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1459,12 +1459,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/12 18:26:46</t>
+          <t>07/12 18:39:01</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>6407</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1486,12 +1486,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/10 18:27:46</t>
+          <t>07/12 18:26:46</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>48049</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1513,12 +1513,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/09 11:40:53</t>
+          <t>07/10 18:27:46</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>56483</t>
+          <t>48049</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1540,12 +1540,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07/06 17:52:23</t>
+          <t>07/09 11:40:53</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>56483</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1567,12 +1567,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07/04 17:10:11</t>
+          <t>07/06 17:52:23</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>20238</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1594,12 +1594,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07/02 19:00:39</t>
+          <t>07/04 17:10:11</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>128241</t>
+          <t>20238</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1621,12 +1621,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07/02 12:32:59</t>
+          <t>07/02 19:00:39</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>128241</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1648,12 +1648,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07/01 16:52:50</t>
+          <t>07/02 12:32:59</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>77108</t>
+          <t>27710</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1675,12 +1675,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06/30 15:16:34</t>
+          <t>07/01 16:52:50</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>72289</t>
+          <t>77108</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1702,12 +1702,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06/30 12:16:11</t>
+          <t>06/30 15:16:34</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>68610</t>
+          <t>72289</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1729,12 +1729,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06/30 11:50:16</t>
+          <t>06/30 12:16:11</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>61000</t>
+          <t>68610</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1756,12 +1756,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06/30 11:35:36</t>
+          <t>06/30 11:50:16</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>79000</t>
+          <t>61000</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1783,12 +1783,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06/29 14:04:21</t>
+          <t>06/30 11:35:36</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>79000</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1810,12 +1810,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06/27 13:07:43</t>
+          <t>06/29 14:04:21</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>42317</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -1837,12 +1837,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06/26 16:07:20</t>
+          <t>06/27 13:07:43</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>42317</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -1864,12 +1864,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06/25 19:22:04</t>
+          <t>06/26 16:07:20</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>48192</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1891,83 +1891,110 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>06/25 19:22:04</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>48192</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
           <t>06/24 14:10:57</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>45524</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
+      <c r="C60" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="60"/>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="61"/>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>7635621</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>920563.94</t>
+          <t>7635621</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>909788</t>
+          <t>920563.94</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>920578</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>10775.94</t>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>-14.06</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/18 15:08:49</t>
+          <t>07/21 19:05:10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>87400</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,22 +90,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>10790.12</t>
+          <t>434.78</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t/>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/17 18:15:22</t>
+          <t>07/18 15:08:49</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>183843</t>
+          <t>87400</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,22 +132,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>21886.07</t>
+          <t>10790.12</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t/>
+          <t>马瑞昭</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/17 17:11:15</t>
+          <t>07/17 18:15:22</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>183843</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,22 +174,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>21886.07</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/14 19:36:37</t>
+          <t>07/17 17:11:15</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,12 +221,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>27710.84</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/12 18:24:59</t>
+          <t>07/14 19:36:37</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,17 +258,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>7407.41</t>
+          <t>27710.84</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t/>
+          <t>马瑞昭</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/10 14:56:17</t>
+          <t>07/12 18:24:59</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>7407.41</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/10 13:45:23</t>
+          <t>07/10 14:56:17</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,17 +342,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>向文</t>
+          <t/>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/09 09:54:13</t>
+          <t>07/10 13:45:23</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,17 +384,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>44578.31</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t>向文</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/09 09:53:40</t>
+          <t>07/09 09:54:13</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,17 +426,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>44578.31</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t/>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -453,7 +453,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/06 16:38:03</t>
+          <t>07/09 09:53:40</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -478,12 +478,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>孔令智</t>
+          <t/>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/04 15:50:29</t>
+          <t>07/06 16:38:03</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -515,12 +515,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>20238.1</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>向超</t>
+          <t>孔令智</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/03 20:29:29</t>
+          <t>07/04 15:50:29</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,39 +552,39 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>20238.1</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t>向超</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>moucai1111</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/02 15:47:40</t>
+          <t>07/03 20:29:29</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1064400</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,39 +594,39 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>128240.96</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t>上海浦东新区 明天上午11</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>moucai1111</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t/>
+          <t>17万 问</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/02 09:17:34</t>
+          <t>07/02 15:47:40</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>1064400</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -641,17 +641,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>27710.84</t>
+          <t>128240.96</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>王志宽</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/01 18:40:00</t>
+          <t>07/02 09:17:34</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,22 +678,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>27710.84</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 安徽 明天 9.00</t>
+          <t>王志宽</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>nn40007</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/01 15:40:01</t>
+          <t>07/01 18:40:00</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,22 +720,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>林伟超</t>
+          <t>:安徽省阜阳市临泉县杨桥镇 安徽 明天 9.00</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>nn40007</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/01 14:50:11</t>
+          <t>07/01 15:40:01</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -767,17 +767,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>46987.95</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>向文</t>
+          <t>林伟超</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06/30 13:54:57</t>
+          <t>07/01 14:50:11</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -809,17 +809,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>33734.94</t>
+          <t>46987.95</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>向文</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06/30 13:00:19</t>
+          <t>06/30 13:54:57</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -851,12 +851,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>38554.22</t>
+          <t>33734.94</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>李志伟</t>
+          <t>马瑞昭</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06/30 10:47:16</t>
+          <t>06/30 13:00:19</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>33734.94</t>
+          <t>38554.22</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>耿振云</t>
+          <t>李志伟</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06/30 10:22:52</t>
+          <t>06/30 10:47:16</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,17 +930,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>114634.15</t>
+          <t>33734.94</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t/>
+          <t>耿振云</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06/30 10:08:02</t>
+          <t>06/30 10:22:52</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,17 +972,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>114634.15</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06/29 12:46:37</t>
+          <t>06/30 10:08:02</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1019,12 +1019,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>林伟超</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06/27 13:03:05</t>
+          <t>06/29 12:46:37</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,17 +1056,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>6172.84</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t/>
+          <t>林伟超</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06/27 11:42:49</t>
+          <t>06/27 13:03:05</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>6172.84</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06/26 14:40:59</t>
+          <t>06/27 11:42:49</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06/25 16:34:17</t>
+          <t>06/26 14:40:59</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1182,17 +1182,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>48192.77</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06/24 12:36:33</t>
+          <t>06/25 16:34:17</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1224,17 +1224,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>21428.57</t>
+          <t>48192.77</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1251,166 +1251,181 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>06/24 12:36:33</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>180000</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>21428.57</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>马瑞昭</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>06/24 12:08:55</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>24096.39</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>羊美云</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="34"/>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="37"/>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="38"/>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/18 17:18:15</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>10790</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/17 19:45:53</t>
+          <t>07/18 17:18:15</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>52006</t>
+          <t>10790</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1432,12 +1447,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/14 20:52:08</t>
+          <t>07/17 19:45:53</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>52006</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1447,7 +1462,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1459,12 +1474,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/12 18:39:01</t>
+          <t>07/14 20:52:08</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>6407</t>
+          <t>27710</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1486,12 +1501,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/12 18:26:46</t>
+          <t>07/12 18:39:01</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>6407</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1513,12 +1528,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/10 18:27:46</t>
+          <t>07/12 18:26:46</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>48049</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1528,7 +1543,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1540,12 +1555,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07/09 11:40:53</t>
+          <t>07/10 18:27:46</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>56483</t>
+          <t>48049</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1567,12 +1582,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07/06 17:52:23</t>
+          <t>07/09 11:40:53</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>56483</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1594,12 +1609,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07/04 17:10:11</t>
+          <t>07/06 17:52:23</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>20238</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1621,12 +1636,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07/02 19:00:39</t>
+          <t>07/04 17:10:11</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>128241</t>
+          <t>20238</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1648,12 +1663,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07/02 12:32:59</t>
+          <t>07/02 19:00:39</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>128241</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1675,12 +1690,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07/01 16:52:50</t>
+          <t>07/02 12:32:59</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>77108</t>
+          <t>27710</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1702,12 +1717,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06/30 15:16:34</t>
+          <t>07/01 16:52:50</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>72289</t>
+          <t>77108</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1729,12 +1744,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06/30 12:16:11</t>
+          <t>06/30 15:16:34</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>68610</t>
+          <t>72289</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1744,7 +1759,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1756,12 +1771,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06/30 11:50:16</t>
+          <t>06/30 12:16:11</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>61000</t>
+          <t>68610</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1771,7 +1786,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -1783,12 +1798,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06/30 11:35:36</t>
+          <t>06/30 11:50:16</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>79000</t>
+          <t>61000</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1810,12 +1825,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06/29 14:04:21</t>
+          <t>06/30 11:35:36</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>79000</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1837,12 +1852,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06/27 13:07:43</t>
+          <t>06/29 14:04:21</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>42317</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1852,7 +1867,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -1864,12 +1879,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06/26 16:07:20</t>
+          <t>06/27 13:07:43</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>42317</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1879,7 +1894,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -1891,12 +1906,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06/25 19:22:04</t>
+          <t>06/26 16:07:20</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>48192</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1918,83 +1933,110 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
+          <t>06/25 19:22:04</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>48192</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
           <t>06/24 14:10:57</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>45524</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="61"/>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="62"/>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>7635621</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>920563.94</t>
+          <t>7640621</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>920578</t>
+          <t>920998.72</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>920578</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>-14.06</t>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>420.72</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
@@ -1420,12 +1420,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/18 17:18:15</t>
+          <t>07/21 20:19:37</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>10790</t>
+          <t>434</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1447,12 +1447,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/17 19:45:53</t>
+          <t>07/18 17:18:15</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>52006</t>
+          <t>10790</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1474,12 +1474,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/14 20:52:08</t>
+          <t>07/17 19:45:53</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>52006</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1501,12 +1501,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/12 18:39:01</t>
+          <t>07/14 20:52:08</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>6407</t>
+          <t>27710</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1528,12 +1528,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/12 18:26:46</t>
+          <t>07/12 18:39:01</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>6407</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1555,12 +1555,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07/10 18:27:46</t>
+          <t>07/12 18:26:46</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>48049</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1582,12 +1582,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07/09 11:40:53</t>
+          <t>07/10 18:27:46</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>56483</t>
+          <t>48049</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1609,12 +1609,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07/06 17:52:23</t>
+          <t>07/09 11:40:53</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>56483</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1636,12 +1636,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07/04 17:10:11</t>
+          <t>07/06 17:52:23</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>20238</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1663,12 +1663,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07/02 19:00:39</t>
+          <t>07/04 17:10:11</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>128241</t>
+          <t>20238</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1690,12 +1690,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07/02 12:32:59</t>
+          <t>07/02 19:00:39</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>128241</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1717,12 +1717,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07/01 16:52:50</t>
+          <t>07/02 12:32:59</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>77108</t>
+          <t>27710</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1744,12 +1744,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06/30 15:16:34</t>
+          <t>07/01 16:52:50</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>72289</t>
+          <t>77108</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1771,12 +1771,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06/30 12:16:11</t>
+          <t>06/30 15:16:34</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>68610</t>
+          <t>72289</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -1798,12 +1798,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06/30 11:50:16</t>
+          <t>06/30 12:16:11</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>61000</t>
+          <t>68610</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -1825,12 +1825,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06/30 11:35:36</t>
+          <t>06/30 11:50:16</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>79000</t>
+          <t>61000</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1852,12 +1852,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06/29 14:04:21</t>
+          <t>06/30 11:35:36</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>79000</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1879,12 +1879,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06/27 13:07:43</t>
+          <t>06/29 14:04:21</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>42317</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -1906,12 +1906,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06/26 16:07:20</t>
+          <t>06/27 13:07:43</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>42317</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -1933,12 +1933,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06/25 19:22:04</t>
+          <t>06/26 16:07:20</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>48192</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1960,83 +1960,110 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>06/25 19:22:04</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>48192</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
           <t>06/24 14:10:57</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>45524</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="62"/>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="63"/>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>7640621</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>920998.72</t>
+          <t>7640621</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>920578</t>
+          <t>920998.72</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>921012</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>420.72</t>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>-13.28</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/21 19:05:10</t>
+          <t>07/22 14:50:15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,17 +90,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>434.78</t>
+          <t>27380.95</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t/>
+          <t>耿振云</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/18 15:08:49</t>
+          <t>07/21 19:05:10</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>87400</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,22 +132,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>10790.12</t>
+          <t>434.78</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t/>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/17 18:15:22</t>
+          <t>07/18 15:08:49</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>183843</t>
+          <t>87400</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,22 +174,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>21886.07</t>
+          <t>10790.12</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t/>
+          <t>马瑞昭</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/17 17:11:15</t>
+          <t>07/17 18:15:22</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>183843</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,22 +216,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>21886.07</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/14 19:36:37</t>
+          <t>07/17 17:11:15</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,12 +263,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>27710.84</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/12 18:24:59</t>
+          <t>07/14 19:36:37</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,17 +300,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>7407.41</t>
+          <t>27710.84</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t/>
+          <t>马瑞昭</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/10 14:56:17</t>
+          <t>07/12 18:24:59</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>7407.41</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/10 13:45:23</t>
+          <t>07/10 14:56:17</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,17 +384,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>向文</t>
+          <t/>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/09 09:54:13</t>
+          <t>07/10 13:45:23</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,17 +426,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>44578.31</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t>向文</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/09 09:53:40</t>
+          <t>07/09 09:54:13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,17 +468,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>44578.31</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t/>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -495,7 +495,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/06 16:38:03</t>
+          <t>07/09 09:53:40</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -520,12 +520,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>孔令智</t>
+          <t/>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/04 15:50:29</t>
+          <t>07/06 16:38:03</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -557,12 +557,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>20238.1</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>向超</t>
+          <t>孔令智</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/03 20:29:29</t>
+          <t>07/04 15:50:29</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,39 +594,39 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>20238.1</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t>向超</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>moucai1111</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/02 15:47:40</t>
+          <t>07/03 20:29:29</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1064400</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,39 +636,39 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>128240.96</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t>上海浦东新区 明天上午11</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>moucai1111</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t/>
+          <t>17万 问</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/02 09:17:34</t>
+          <t>07/02 15:47:40</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>1064400</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -683,17 +683,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>27710.84</t>
+          <t>128240.96</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>王志宽</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/01 18:40:00</t>
+          <t>07/02 09:17:34</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,22 +720,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>27710.84</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 安徽 明天 9.00</t>
+          <t>王志宽</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>nn40007</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/01 15:40:01</t>
+          <t>07/01 18:40:00</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,22 +762,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>林伟超</t>
+          <t>:安徽省阜阳市临泉县杨桥镇 安徽 明天 9.00</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>nn40007</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/01 14:50:11</t>
+          <t>07/01 15:40:01</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -809,17 +809,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>46987.95</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>向文</t>
+          <t>林伟超</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06/30 13:54:57</t>
+          <t>07/01 14:50:11</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -851,17 +851,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>33734.94</t>
+          <t>46987.95</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>向文</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06/30 13:00:19</t>
+          <t>06/30 13:54:57</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>38554.22</t>
+          <t>33734.94</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>李志伟</t>
+          <t>马瑞昭</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06/30 10:47:16</t>
+          <t>06/30 13:00:19</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -935,12 +935,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>33734.94</t>
+          <t>38554.22</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>耿振云</t>
+          <t>李志伟</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06/30 10:22:52</t>
+          <t>06/30 10:47:16</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,17 +972,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>114634.15</t>
+          <t>33734.94</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t/>
+          <t>耿振云</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06/30 10:08:02</t>
+          <t>06/30 10:22:52</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,17 +1014,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>114634.15</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06/29 12:46:37</t>
+          <t>06/30 10:08:02</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1061,12 +1061,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>林伟超</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06/27 13:03:05</t>
+          <t>06/29 12:46:37</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,17 +1098,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>6172.84</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t/>
+          <t>林伟超</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06/27 11:42:49</t>
+          <t>06/27 13:03:05</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>6172.84</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06/26 14:40:59</t>
+          <t>06/27 11:42:49</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06/25 16:34:17</t>
+          <t>06/26 14:40:59</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1224,17 +1224,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>48192.77</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06/24 12:36:33</t>
+          <t>06/25 16:34:17</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1266,17 +1266,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>21428.57</t>
+          <t>48192.77</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1293,166 +1293,181 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>06/24 12:36:33</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>180000</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>21428.57</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>马瑞昭</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>06/24 12:08:55</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>24096.39</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>羊美云</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="36"/>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="38"/>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/21 20:19:37</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/18 17:18:15</t>
+          <t>07/21 20:19:37</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>10790</t>
+          <t>434</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1462,7 +1477,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1474,12 +1489,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/17 19:45:53</t>
+          <t>07/18 17:18:15</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>52006</t>
+          <t>10790</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1501,12 +1516,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/14 20:52:08</t>
+          <t>07/17 19:45:53</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>52006</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1516,7 +1531,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1528,12 +1543,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/12 18:39:01</t>
+          <t>07/14 20:52:08</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>6407</t>
+          <t>27710</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1555,12 +1570,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07/12 18:26:46</t>
+          <t>07/12 18:39:01</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>6407</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1582,12 +1597,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07/10 18:27:46</t>
+          <t>07/12 18:26:46</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>48049</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1597,7 +1612,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1609,12 +1624,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07/09 11:40:53</t>
+          <t>07/10 18:27:46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>56483</t>
+          <t>48049</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1636,12 +1651,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07/06 17:52:23</t>
+          <t>07/09 11:40:53</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>56483</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1663,12 +1678,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07/04 17:10:11</t>
+          <t>07/06 17:52:23</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>20238</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1690,12 +1705,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07/02 19:00:39</t>
+          <t>07/04 17:10:11</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>128241</t>
+          <t>20238</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1717,12 +1732,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07/02 12:32:59</t>
+          <t>07/02 19:00:39</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>128241</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1744,12 +1759,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07/01 16:52:50</t>
+          <t>07/02 12:32:59</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>77108</t>
+          <t>27710</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1771,12 +1786,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06/30 15:16:34</t>
+          <t>07/01 16:52:50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>72289</t>
+          <t>77108</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1798,12 +1813,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06/30 12:16:11</t>
+          <t>06/30 15:16:34</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>68610</t>
+          <t>72289</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1813,7 +1828,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -1825,12 +1840,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06/30 11:50:16</t>
+          <t>06/30 12:16:11</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>61000</t>
+          <t>68610</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1840,7 +1855,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -1852,12 +1867,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06/30 11:35:36</t>
+          <t>06/30 11:50:16</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>79000</t>
+          <t>61000</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1879,12 +1894,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06/29 14:04:21</t>
+          <t>06/30 11:35:36</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>79000</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1906,12 +1921,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06/27 13:07:43</t>
+          <t>06/29 14:04:21</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>42317</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1921,7 +1936,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -1933,12 +1948,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06/26 16:07:20</t>
+          <t>06/27 13:07:43</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>42317</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1948,7 +1963,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -1960,12 +1975,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>06/25 19:22:04</t>
+          <t>06/26 16:07:20</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>48192</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1987,83 +2002,110 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>06/25 19:22:04</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>48192</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
           <t>06/24 14:10:57</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>45524</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="63"/>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="64"/>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>7640621</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>920998.72</t>
+          <t>7870621</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>921012</t>
+          <t>948379.68</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>921012</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>-13.28</t>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>27367.68</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/22 14:50:15</t>
+          <t>07/22 14:51:36</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>44950</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>27380.95</t>
+          <t>5351.19</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/21 19:05:10</t>
+          <t>07/22 14:50:15</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,17 +132,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>434.78</t>
+          <t>27380.95</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t/>
+          <t>耿振云</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/18 15:08:49</t>
+          <t>07/21 19:05:10</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>87400</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,22 +174,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>10790.12</t>
+          <t>434.78</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t/>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/17 18:15:22</t>
+          <t>07/18 15:08:49</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>183843</t>
+          <t>87400</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,22 +216,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>21886.07</t>
+          <t>10790.12</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t/>
+          <t>马瑞昭</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/17 17:11:15</t>
+          <t>07/17 18:15:22</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>183843</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,22 +258,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>21886.07</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/14 19:36:37</t>
+          <t>07/17 17:11:15</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,12 +305,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>27710.84</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/12 18:24:59</t>
+          <t>07/14 19:36:37</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,17 +342,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>7407.41</t>
+          <t>27710.84</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t/>
+          <t>马瑞昭</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/10 14:56:17</t>
+          <t>07/12 18:24:59</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>7407.41</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/10 13:45:23</t>
+          <t>07/10 14:56:17</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,17 +426,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>向文</t>
+          <t/>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/09 09:54:13</t>
+          <t>07/10 13:45:23</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,17 +468,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>44578.31</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t>向文</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/09 09:53:40</t>
+          <t>07/09 09:54:13</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,17 +510,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>44578.31</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t/>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -537,7 +537,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/06 16:38:03</t>
+          <t>07/09 09:53:40</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -562,12 +562,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>孔令智</t>
+          <t/>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/04 15:50:29</t>
+          <t>07/06 16:38:03</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -599,12 +599,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>20238.1</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>向超</t>
+          <t>孔令智</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/03 20:29:29</t>
+          <t>07/04 15:50:29</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,39 +636,39 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>20238.1</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t>向超</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>moucai1111</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/02 15:47:40</t>
+          <t>07/03 20:29:29</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1064400</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,39 +678,39 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>128240.96</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t>上海浦东新区 明天上午11</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>moucai1111</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t/>
+          <t>17万 问</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/02 09:17:34</t>
+          <t>07/02 15:47:40</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>1064400</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -725,17 +725,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>27710.84</t>
+          <t>128240.96</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>王志宽</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/01 18:40:00</t>
+          <t>07/02 09:17:34</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,22 +762,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>27710.84</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 安徽 明天 9.00</t>
+          <t>王志宽</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>nn40007</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/01 15:40:01</t>
+          <t>07/01 18:40:00</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,22 +804,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>林伟超</t>
+          <t>:安徽省阜阳市临泉县杨桥镇 安徽 明天 9.00</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>nn40007</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/01 14:50:11</t>
+          <t>07/01 15:40:01</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -851,17 +851,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>46987.95</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>向文</t>
+          <t>林伟超</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06/30 13:54:57</t>
+          <t>07/01 14:50:11</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -893,17 +893,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>33734.94</t>
+          <t>46987.95</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>向文</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06/30 13:00:19</t>
+          <t>06/30 13:54:57</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -935,12 +935,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>38554.22</t>
+          <t>33734.94</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>李志伟</t>
+          <t>马瑞昭</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06/30 10:47:16</t>
+          <t>06/30 13:00:19</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -977,12 +977,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>33734.94</t>
+          <t>38554.22</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>耿振云</t>
+          <t>李志伟</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06/30 10:22:52</t>
+          <t>06/30 10:47:16</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,17 +1014,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>114634.15</t>
+          <t>33734.94</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t/>
+          <t>耿振云</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06/30 10:08:02</t>
+          <t>06/30 10:22:52</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,17 +1056,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>114634.15</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06/29 12:46:37</t>
+          <t>06/30 10:08:02</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>林伟超</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06/27 13:03:05</t>
+          <t>06/29 12:46:37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,17 +1140,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>6172.84</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t/>
+          <t>林伟超</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06/27 11:42:49</t>
+          <t>06/27 13:03:05</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>6172.84</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06/26 14:40:59</t>
+          <t>06/27 11:42:49</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06/25 16:34:17</t>
+          <t>06/26 14:40:59</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1266,17 +1266,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>48192.77</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06/24 12:36:33</t>
+          <t>06/25 16:34:17</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1308,17 +1308,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>21428.57</t>
+          <t>48192.77</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1335,166 +1335,181 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>06/24 12:36:33</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>180000</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>21428.57</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>马瑞昭</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>06/24 12:08:55</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>24096.39</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>羊美云</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="36"/>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="39"/>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/21 20:19:37</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/18 17:18:15</t>
+          <t>07/21 20:19:37</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>10790</t>
+          <t>434</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1504,7 +1519,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1516,12 +1531,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/17 19:45:53</t>
+          <t>07/18 17:18:15</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>52006</t>
+          <t>10790</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1543,12 +1558,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/14 20:52:08</t>
+          <t>07/17 19:45:53</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>52006</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1558,7 +1573,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1570,12 +1585,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07/12 18:39:01</t>
+          <t>07/14 20:52:08</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>6407</t>
+          <t>27710</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1597,12 +1612,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07/12 18:26:46</t>
+          <t>07/12 18:39:01</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>6407</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1624,12 +1639,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07/10 18:27:46</t>
+          <t>07/12 18:26:46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>48049</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1639,7 +1654,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1651,12 +1666,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07/09 11:40:53</t>
+          <t>07/10 18:27:46</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>56483</t>
+          <t>48049</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1678,12 +1693,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07/06 17:52:23</t>
+          <t>07/09 11:40:53</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>56483</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1705,12 +1720,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07/04 17:10:11</t>
+          <t>07/06 17:52:23</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>20238</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1732,12 +1747,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07/02 19:00:39</t>
+          <t>07/04 17:10:11</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>128241</t>
+          <t>20238</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1759,12 +1774,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07/02 12:32:59</t>
+          <t>07/02 19:00:39</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>128241</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1786,12 +1801,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07/01 16:52:50</t>
+          <t>07/02 12:32:59</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>77108</t>
+          <t>27710</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1813,12 +1828,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06/30 15:16:34</t>
+          <t>07/01 16:52:50</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>72289</t>
+          <t>77108</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1840,12 +1855,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06/30 12:16:11</t>
+          <t>06/30 15:16:34</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>68610</t>
+          <t>72289</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1855,7 +1870,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -1867,12 +1882,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06/30 11:50:16</t>
+          <t>06/30 12:16:11</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>61000</t>
+          <t>68610</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1882,7 +1897,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -1894,12 +1909,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06/30 11:35:36</t>
+          <t>06/30 11:50:16</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>79000</t>
+          <t>61000</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1921,12 +1936,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06/29 14:04:21</t>
+          <t>06/30 11:35:36</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>79000</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1948,12 +1963,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06/27 13:07:43</t>
+          <t>06/29 14:04:21</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>42317</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1963,7 +1978,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -1975,12 +1990,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>06/26 16:07:20</t>
+          <t>06/27 13:07:43</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>42317</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1990,7 +2005,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2002,12 +2017,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>06/25 19:22:04</t>
+          <t>06/26 16:07:20</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>48192</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2029,83 +2044,110 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>06/25 19:22:04</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>48192</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
           <t>06/24 14:10:57</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>45524</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="64"/>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="65"/>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>7870621</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>948379.68</t>
+          <t>7915571</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>921012</t>
+          <t>953730.87</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>921012</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>27367.68</t>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>32718.87</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
@@ -1504,12 +1504,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/21 20:19:37</t>
+          <t>07/22 16:14:19</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>32732</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1531,12 +1531,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/18 17:18:15</t>
+          <t>07/21 20:19:37</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>10790</t>
+          <t>434</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1558,12 +1558,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/17 19:45:53</t>
+          <t>07/18 17:18:15</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>52006</t>
+          <t>10790</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1585,12 +1585,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07/14 20:52:08</t>
+          <t>07/17 19:45:53</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>52006</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1612,12 +1612,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07/12 18:39:01</t>
+          <t>07/14 20:52:08</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>6407</t>
+          <t>27710</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1639,12 +1639,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07/12 18:26:46</t>
+          <t>07/12 18:39:01</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>6407</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1666,12 +1666,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07/10 18:27:46</t>
+          <t>07/12 18:26:46</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>48049</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1693,12 +1693,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07/09 11:40:53</t>
+          <t>07/10 18:27:46</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>56483</t>
+          <t>48049</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1720,12 +1720,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07/06 17:52:23</t>
+          <t>07/09 11:40:53</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>56483</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1747,12 +1747,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07/04 17:10:11</t>
+          <t>07/06 17:52:23</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>20238</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1774,12 +1774,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07/02 19:00:39</t>
+          <t>07/04 17:10:11</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>128241</t>
+          <t>20238</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1801,12 +1801,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07/02 12:32:59</t>
+          <t>07/02 19:00:39</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>128241</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1828,12 +1828,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07/01 16:52:50</t>
+          <t>07/02 12:32:59</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>77108</t>
+          <t>27710</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1855,12 +1855,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06/30 15:16:34</t>
+          <t>07/01 16:52:50</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>72289</t>
+          <t>77108</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1882,12 +1882,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06/30 12:16:11</t>
+          <t>06/30 15:16:34</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>68610</t>
+          <t>72289</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -1909,12 +1909,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06/30 11:50:16</t>
+          <t>06/30 12:16:11</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>61000</t>
+          <t>68610</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -1936,12 +1936,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06/30 11:35:36</t>
+          <t>06/30 11:50:16</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>79000</t>
+          <t>61000</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1963,12 +1963,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06/29 14:04:21</t>
+          <t>06/30 11:35:36</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>79000</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1990,12 +1990,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>06/27 13:07:43</t>
+          <t>06/29 14:04:21</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>42317</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2017,12 +2017,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>06/26 16:07:20</t>
+          <t>06/27 13:07:43</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>42317</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2044,12 +2044,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>06/25 19:22:04</t>
+          <t>06/26 16:07:20</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>48192</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2071,83 +2071,110 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
+          <t>06/25 19:22:04</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>48192</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
           <t>06/24 14:10:57</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>45524</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="65"/>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="66"/>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>7915571</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>953730.87</t>
+          <t>7915571</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>921012</t>
+          <t>953730.87</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>953744</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>32718.87</t>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>-13.13</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/22 14:51:36</t>
+          <t>07/23 09:59:06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>44950</t>
+          <t>420000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,12 +95,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5351.19</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>耿振云</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/22 14:50:15</t>
+          <t>07/22 14:51:36</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>44950</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>27380.95</t>
+          <t>5351.19</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/21 19:05:10</t>
+          <t>07/22 14:50:15</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,17 +174,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>434.78</t>
+          <t>27380.95</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t/>
+          <t>耿振云</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/18 15:08:49</t>
+          <t>07/21 19:05:10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>87400</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,22 +216,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>10790.12</t>
+          <t>434.78</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t/>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/17 18:15:22</t>
+          <t>07/18 15:08:49</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>183843</t>
+          <t>87400</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,22 +258,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>21886.07</t>
+          <t>10790.12</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t/>
+          <t>马瑞昭</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/17 17:11:15</t>
+          <t>07/17 18:15:22</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>183843</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,22 +300,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>21886.07</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/14 19:36:37</t>
+          <t>07/17 17:11:15</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,12 +347,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>27710.84</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/12 18:24:59</t>
+          <t>07/14 19:36:37</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,17 +384,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>7407.41</t>
+          <t>27710.84</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t/>
+          <t>马瑞昭</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/10 14:56:17</t>
+          <t>07/12 18:24:59</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>7407.41</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/10 13:45:23</t>
+          <t>07/10 14:56:17</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,17 +468,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>向文</t>
+          <t/>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/09 09:54:13</t>
+          <t>07/10 13:45:23</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,17 +510,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>44578.31</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t>向文</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/09 09:53:40</t>
+          <t>07/09 09:54:13</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,17 +552,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>44578.31</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t/>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -579,7 +579,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/06 16:38:03</t>
+          <t>07/09 09:53:40</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -604,12 +604,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>孔令智</t>
+          <t/>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/04 15:50:29</t>
+          <t>07/06 16:38:03</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -641,12 +641,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>20238.1</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>向超</t>
+          <t>孔令智</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/03 20:29:29</t>
+          <t>07/04 15:50:29</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,39 +678,39 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>20238.1</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t>向超</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>moucai1111</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/02 15:47:40</t>
+          <t>07/03 20:29:29</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1064400</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,39 +720,39 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>128240.96</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t>上海浦东新区 明天上午11</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>moucai1111</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t/>
+          <t>17万 问</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/02 09:17:34</t>
+          <t>07/02 15:47:40</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>1064400</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -767,17 +767,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>27710.84</t>
+          <t>128240.96</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>王志宽</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/01 18:40:00</t>
+          <t>07/02 09:17:34</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,22 +804,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>27710.84</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 安徽 明天 9.00</t>
+          <t>王志宽</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>nn40007</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/01 15:40:01</t>
+          <t>07/01 18:40:00</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,22 +846,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>林伟超</t>
+          <t>:安徽省阜阳市临泉县杨桥镇 安徽 明天 9.00</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>nn40007</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/01 14:50:11</t>
+          <t>07/01 15:40:01</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -893,17 +893,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>46987.95</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>向文</t>
+          <t>林伟超</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06/30 13:54:57</t>
+          <t>07/01 14:50:11</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -935,17 +935,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>33734.94</t>
+          <t>46987.95</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>向文</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06/30 13:00:19</t>
+          <t>06/30 13:54:57</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -977,12 +977,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>38554.22</t>
+          <t>33734.94</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>李志伟</t>
+          <t>马瑞昭</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06/30 10:47:16</t>
+          <t>06/30 13:00:19</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1019,12 +1019,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>33734.94</t>
+          <t>38554.22</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>耿振云</t>
+          <t>李志伟</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06/30 10:22:52</t>
+          <t>06/30 10:47:16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,17 +1056,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>114634.15</t>
+          <t>33734.94</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t/>
+          <t>耿振云</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06/30 10:08:02</t>
+          <t>06/30 10:22:52</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,17 +1098,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>114634.15</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06/29 12:46:37</t>
+          <t>06/30 10:08:02</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>林伟超</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06/27 13:03:05</t>
+          <t>06/29 12:46:37</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1182,17 +1182,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>6172.84</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t/>
+          <t>林伟超</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06/27 11:42:49</t>
+          <t>06/27 13:03:05</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>6172.84</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06/26 14:40:59</t>
+          <t>06/27 11:42:49</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06/25 16:34:17</t>
+          <t>06/26 14:40:59</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1308,17 +1308,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>48192.77</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1335,12 +1335,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06/24 12:36:33</t>
+          <t>06/25 16:34:17</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1350,17 +1350,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>21428.57</t>
+          <t>48192.77</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1377,166 +1377,181 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>06/24 12:36:33</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>180000</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>21428.57</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>马瑞昭</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>06/24 12:08:55</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>24096.39</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>羊美云</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="37"/>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="38"/>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="40"/>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="41"/>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/22 16:14:19</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>32732</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/21 20:19:37</t>
+          <t>07/22 16:14:19</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>32732</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1546,7 +1561,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1558,12 +1573,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/18 17:18:15</t>
+          <t>07/21 20:19:37</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>10790</t>
+          <t>434</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1573,7 +1588,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1585,12 +1600,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07/17 19:45:53</t>
+          <t>07/18 17:18:15</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>52006</t>
+          <t>10790</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1612,12 +1627,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07/14 20:52:08</t>
+          <t>07/17 19:45:53</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>52006</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1627,7 +1642,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1639,12 +1654,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07/12 18:39:01</t>
+          <t>07/14 20:52:08</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>6407</t>
+          <t>27710</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1666,12 +1681,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07/12 18:26:46</t>
+          <t>07/12 18:39:01</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>6407</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1693,12 +1708,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07/10 18:27:46</t>
+          <t>07/12 18:26:46</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>48049</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1708,7 +1723,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1720,12 +1735,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07/09 11:40:53</t>
+          <t>07/10 18:27:46</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>56483</t>
+          <t>48049</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1747,12 +1762,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07/06 17:52:23</t>
+          <t>07/09 11:40:53</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>56483</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1774,12 +1789,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07/04 17:10:11</t>
+          <t>07/06 17:52:23</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>20238</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1801,12 +1816,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07/02 19:00:39</t>
+          <t>07/04 17:10:11</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>128241</t>
+          <t>20238</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1828,12 +1843,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07/02 12:32:59</t>
+          <t>07/02 19:00:39</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>128241</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1855,12 +1870,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07/01 16:52:50</t>
+          <t>07/02 12:32:59</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>77108</t>
+          <t>27710</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1882,12 +1897,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06/30 15:16:34</t>
+          <t>07/01 16:52:50</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>72289</t>
+          <t>77108</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1909,12 +1924,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06/30 12:16:11</t>
+          <t>06/30 15:16:34</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>68610</t>
+          <t>72289</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1924,7 +1939,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -1936,12 +1951,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06/30 11:50:16</t>
+          <t>06/30 12:16:11</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>61000</t>
+          <t>68610</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1951,7 +1966,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -1963,12 +1978,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06/30 11:35:36</t>
+          <t>06/30 11:50:16</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>79000</t>
+          <t>61000</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1990,12 +2005,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>06/29 14:04:21</t>
+          <t>06/30 11:35:36</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>79000</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2017,12 +2032,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>06/27 13:07:43</t>
+          <t>06/29 14:04:21</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>42317</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2032,7 +2047,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2044,12 +2059,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>06/26 16:07:20</t>
+          <t>06/27 13:07:43</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>42317</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2059,7 +2074,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2071,12 +2086,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>06/25 19:22:04</t>
+          <t>06/26 16:07:20</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>48192</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2098,83 +2113,110 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
+          <t>06/25 19:22:04</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>48192</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
           <t>06/24 14:10:57</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>45524</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="66"/>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="67"/>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>7915571</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>953730.87</t>
+          <t>8335571</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>953744</t>
+          <t>1003730.87</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>953744</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>-13.13</t>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>49986.87</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
@@ -1546,12 +1546,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/22 16:14:19</t>
+          <t>07/23 12:09:30</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>32732</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1573,12 +1573,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/21 20:19:37</t>
+          <t>07/22 16:14:19</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>32732</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1600,12 +1600,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07/18 17:18:15</t>
+          <t>07/21 20:19:37</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>10790</t>
+          <t>434</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1627,12 +1627,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07/17 19:45:53</t>
+          <t>07/18 17:18:15</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>52006</t>
+          <t>10790</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1654,12 +1654,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07/14 20:52:08</t>
+          <t>07/17 19:45:53</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>52006</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1681,12 +1681,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07/12 18:39:01</t>
+          <t>07/14 20:52:08</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>6407</t>
+          <t>27710</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1708,12 +1708,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07/12 18:26:46</t>
+          <t>07/12 18:39:01</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>6407</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1735,12 +1735,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07/10 18:27:46</t>
+          <t>07/12 18:26:46</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>48049</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1762,12 +1762,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07/09 11:40:53</t>
+          <t>07/10 18:27:46</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>56483</t>
+          <t>48049</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1789,12 +1789,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07/06 17:52:23</t>
+          <t>07/09 11:40:53</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>56483</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1816,12 +1816,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07/04 17:10:11</t>
+          <t>07/06 17:52:23</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>20238</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1843,12 +1843,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07/02 19:00:39</t>
+          <t>07/04 17:10:11</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>128241</t>
+          <t>20238</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1870,12 +1870,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07/02 12:32:59</t>
+          <t>07/02 19:00:39</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>128241</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1897,12 +1897,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07/01 16:52:50</t>
+          <t>07/02 12:32:59</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>77108</t>
+          <t>27710</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1924,12 +1924,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06/30 15:16:34</t>
+          <t>07/01 16:52:50</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>72289</t>
+          <t>77108</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1951,12 +1951,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06/30 12:16:11</t>
+          <t>06/30 15:16:34</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>68610</t>
+          <t>72289</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -1978,12 +1978,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06/30 11:50:16</t>
+          <t>06/30 12:16:11</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>61000</t>
+          <t>68610</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2005,12 +2005,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>06/30 11:35:36</t>
+          <t>06/30 11:50:16</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>79000</t>
+          <t>61000</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2032,12 +2032,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>06/29 14:04:21</t>
+          <t>06/30 11:35:36</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>79000</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2059,12 +2059,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>06/27 13:07:43</t>
+          <t>06/29 14:04:21</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>42317</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2086,12 +2086,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>06/26 16:07:20</t>
+          <t>06/27 13:07:43</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>42317</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2113,12 +2113,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>06/25 19:22:04</t>
+          <t>06/26 16:07:20</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>48192</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2140,83 +2140,110 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
+          <t>06/25 19:22:04</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>48192</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
           <t>06/24 14:10:57</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>45524</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="67"/>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="68"/>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>8335571</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1003730.87</t>
+          <t>8335571</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>953744</t>
+          <t>1003730.87</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>1003744</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>49986.87</t>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>-13.13</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/23 09:59:06</t>
+          <t>07/25 14:41:17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>420000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,17 +90,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/22 14:51:36</t>
+          <t>07/23 09:59:06</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>44950</t>
+          <t>420000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,12 +137,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>5351.19</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>耿振云</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/22 14:50:15</t>
+          <t>07/22 14:51:36</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>44950</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>27380.95</t>
+          <t>5351.19</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/21 19:05:10</t>
+          <t>07/22 14:50:15</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,17 +216,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>434.78</t>
+          <t>27380.95</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t/>
+          <t>耿振云</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/18 15:08:49</t>
+          <t>07/21 19:05:10</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>87400</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,22 +258,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>10790.12</t>
+          <t>434.78</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t/>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/17 18:15:22</t>
+          <t>07/18 15:08:49</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>183843</t>
+          <t>87400</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,22 +300,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>21886.07</t>
+          <t>10790.12</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t/>
+          <t>马瑞昭</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/17 17:11:15</t>
+          <t>07/17 18:15:22</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>183843</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,22 +342,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>21886.07</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/14 19:36:37</t>
+          <t>07/17 17:11:15</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,12 +389,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>27710.84</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/12 18:24:59</t>
+          <t>07/14 19:36:37</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,17 +426,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>7407.41</t>
+          <t>27710.84</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t/>
+          <t>马瑞昭</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/10 14:56:17</t>
+          <t>07/12 18:24:59</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>7407.41</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/10 13:45:23</t>
+          <t>07/10 14:56:17</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,17 +510,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>向文</t>
+          <t/>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/09 09:54:13</t>
+          <t>07/10 13:45:23</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,17 +552,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>44578.31</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t>向文</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/09 09:53:40</t>
+          <t>07/09 09:54:13</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,17 +594,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>44578.31</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t/>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -621,7 +621,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/06 16:38:03</t>
+          <t>07/09 09:53:40</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>孔令智</t>
+          <t/>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/04 15:50:29</t>
+          <t>07/06 16:38:03</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -683,12 +683,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>20238.1</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>向超</t>
+          <t>孔令智</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/03 20:29:29</t>
+          <t>07/04 15:50:29</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,39 +720,39 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>20238.1</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t>向超</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>moucai1111</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/02 15:47:40</t>
+          <t>07/03 20:29:29</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1064400</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,39 +762,39 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>128240.96</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t>上海浦东新区 明天上午11</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>moucai1111</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t/>
+          <t>17万 问</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/02 09:17:34</t>
+          <t>07/02 15:47:40</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>1064400</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -809,17 +809,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>27710.84</t>
+          <t>128240.96</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>王志宽</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/01 18:40:00</t>
+          <t>07/02 09:17:34</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,22 +846,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>27710.84</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 安徽 明天 9.00</t>
+          <t>王志宽</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>nn40007</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/01 15:40:01</t>
+          <t>07/01 18:40:00</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,22 +888,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>林伟超</t>
+          <t>:安徽省阜阳市临泉县杨桥镇 安徽 明天 9.00</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>nn40007</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/01 14:50:11</t>
+          <t>07/01 15:40:01</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -935,17 +935,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>46987.95</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>向文</t>
+          <t>林伟超</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06/30 13:54:57</t>
+          <t>07/01 14:50:11</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -977,17 +977,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>33734.94</t>
+          <t>46987.95</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>向文</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06/30 13:00:19</t>
+          <t>06/30 13:54:57</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1019,12 +1019,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>38554.22</t>
+          <t>33734.94</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>李志伟</t>
+          <t>马瑞昭</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06/30 10:47:16</t>
+          <t>06/30 13:00:19</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1061,12 +1061,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>33734.94</t>
+          <t>38554.22</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>耿振云</t>
+          <t>李志伟</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06/30 10:22:52</t>
+          <t>06/30 10:47:16</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,17 +1098,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>114634.15</t>
+          <t>33734.94</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t/>
+          <t>耿振云</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06/30 10:08:02</t>
+          <t>06/30 10:22:52</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,17 +1140,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>114634.15</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06/29 12:46:37</t>
+          <t>06/30 10:08:02</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>林伟超</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06/27 13:03:05</t>
+          <t>06/29 12:46:37</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1224,17 +1224,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>6172.84</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t/>
+          <t>林伟超</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06/27 11:42:49</t>
+          <t>06/27 13:03:05</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>6172.84</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06/26 14:40:59</t>
+          <t>06/27 11:42:49</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1335,12 +1335,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06/25 16:34:17</t>
+          <t>06/26 14:40:59</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1350,17 +1350,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>48192.77</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1377,12 +1377,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06/24 12:36:33</t>
+          <t>06/25 16:34:17</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1392,17 +1392,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>21428.57</t>
+          <t>48192.77</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1419,166 +1419,181 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>06/24 12:36:33</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>180000</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>21428.57</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>马瑞昭</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>06/24 12:08:55</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>24096.39</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>羊美云</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="38"/>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="41"/>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/23 12:09:30</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/22 16:14:19</t>
+          <t>07/23 12:09:30</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>32732</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1600,12 +1615,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07/21 20:19:37</t>
+          <t>07/22 16:14:19</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>32732</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1615,7 +1630,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1627,12 +1642,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07/18 17:18:15</t>
+          <t>07/21 20:19:37</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>10790</t>
+          <t>434</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1642,7 +1657,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1654,12 +1669,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07/17 19:45:53</t>
+          <t>07/18 17:18:15</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>52006</t>
+          <t>10790</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1681,12 +1696,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07/14 20:52:08</t>
+          <t>07/17 19:45:53</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>52006</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1696,7 +1711,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1708,12 +1723,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07/12 18:39:01</t>
+          <t>07/14 20:52:08</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>6407</t>
+          <t>27710</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1735,12 +1750,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07/12 18:26:46</t>
+          <t>07/12 18:39:01</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>6407</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1762,12 +1777,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07/10 18:27:46</t>
+          <t>07/12 18:26:46</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>48049</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1777,7 +1792,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1789,12 +1804,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07/09 11:40:53</t>
+          <t>07/10 18:27:46</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>56483</t>
+          <t>48049</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1816,12 +1831,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07/06 17:52:23</t>
+          <t>07/09 11:40:53</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>56483</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1843,12 +1858,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07/04 17:10:11</t>
+          <t>07/06 17:52:23</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>20238</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1870,12 +1885,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07/02 19:00:39</t>
+          <t>07/04 17:10:11</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>128241</t>
+          <t>20238</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1897,12 +1912,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07/02 12:32:59</t>
+          <t>07/02 19:00:39</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>128241</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1924,12 +1939,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07/01 16:52:50</t>
+          <t>07/02 12:32:59</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>77108</t>
+          <t>27710</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1951,12 +1966,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06/30 15:16:34</t>
+          <t>07/01 16:52:50</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>72289</t>
+          <t>77108</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1978,12 +1993,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06/30 12:16:11</t>
+          <t>06/30 15:16:34</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>68610</t>
+          <t>72289</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1993,7 +2008,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2005,12 +2020,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>06/30 11:50:16</t>
+          <t>06/30 12:16:11</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>61000</t>
+          <t>68610</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2020,7 +2035,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2032,12 +2047,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>06/30 11:35:36</t>
+          <t>06/30 11:50:16</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>79000</t>
+          <t>61000</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2059,12 +2074,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>06/29 14:04:21</t>
+          <t>06/30 11:35:36</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>79000</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2086,12 +2101,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>06/27 13:07:43</t>
+          <t>06/29 14:04:21</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>42317</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2101,7 +2116,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2113,12 +2128,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>06/26 16:07:20</t>
+          <t>06/27 13:07:43</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>42317</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2128,7 +2143,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2140,12 +2155,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>06/25 19:22:04</t>
+          <t>06/26 16:07:20</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>48192</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2167,83 +2182,110 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>06/25 19:22:04</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>48192</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
           <t>06/24 14:10:57</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>45524</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="68"/>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="69"/>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>8335571</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1003730.87</t>
+          <t>8435571</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1003744</t>
+          <t>1015495.57</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>1003744</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>-13.13</t>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>11751.57</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/25 14:41:17</t>
+          <t>07/25 19:35:03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>95990</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>11033.33</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/23 09:59:06</t>
+          <t>07/25 14:41:17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>420000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,17 +132,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/22 14:51:36</t>
+          <t>07/23 09:59:06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>44950</t>
+          <t>420000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,12 +179,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>5351.19</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>耿振云</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/22 14:50:15</t>
+          <t>07/22 14:51:36</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>44950</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>27380.95</t>
+          <t>5351.19</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/21 19:05:10</t>
+          <t>07/22 14:50:15</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,17 +258,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>434.78</t>
+          <t>27380.95</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t/>
+          <t>耿振云</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/18 15:08:49</t>
+          <t>07/21 19:05:10</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>87400</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,22 +300,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>10790.12</t>
+          <t>434.78</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t/>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/17 18:15:22</t>
+          <t>07/18 15:08:49</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>183843</t>
+          <t>87400</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,22 +342,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>21886.07</t>
+          <t>10790.12</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t/>
+          <t>马瑞昭</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/17 17:11:15</t>
+          <t>07/17 18:15:22</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>183843</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,22 +384,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>21886.07</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/14 19:36:37</t>
+          <t>07/17 17:11:15</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -431,12 +431,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>27710.84</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/12 18:24:59</t>
+          <t>07/14 19:36:37</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,17 +468,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>7407.41</t>
+          <t>27710.84</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t/>
+          <t>马瑞昭</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/10 14:56:17</t>
+          <t>07/12 18:24:59</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>7407.41</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/10 13:45:23</t>
+          <t>07/10 14:56:17</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,17 +552,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>向文</t>
+          <t/>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/09 09:54:13</t>
+          <t>07/10 13:45:23</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,17 +594,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>44578.31</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t>向文</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/09 09:53:40</t>
+          <t>07/09 09:54:13</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,17 +636,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>44578.31</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t/>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -663,7 +663,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/06 16:38:03</t>
+          <t>07/09 09:53:40</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -688,12 +688,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>孔令智</t>
+          <t/>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/04 15:50:29</t>
+          <t>07/06 16:38:03</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -725,12 +725,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>20238.1</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>向超</t>
+          <t>孔令智</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/03 20:29:29</t>
+          <t>07/04 15:50:29</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,39 +762,39 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>20238.1</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t>向超</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>moucai1111</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/02 15:47:40</t>
+          <t>07/03 20:29:29</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1064400</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,39 +804,39 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>128240.96</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t>上海浦东新区 明天上午11</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>moucai1111</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t/>
+          <t>17万 问</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/02 09:17:34</t>
+          <t>07/02 15:47:40</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>1064400</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -851,17 +851,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>27710.84</t>
+          <t>128240.96</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>王志宽</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/01 18:40:00</t>
+          <t>07/02 09:17:34</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,22 +888,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>27710.84</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 安徽 明天 9.00</t>
+          <t>王志宽</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>nn40007</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/01 15:40:01</t>
+          <t>07/01 18:40:00</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,22 +930,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>林伟超</t>
+          <t>:安徽省阜阳市临泉县杨桥镇 安徽 明天 9.00</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>nn40007</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/01 14:50:11</t>
+          <t>07/01 15:40:01</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -977,17 +977,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>46987.95</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>向文</t>
+          <t>林伟超</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06/30 13:54:57</t>
+          <t>07/01 14:50:11</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1019,17 +1019,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>33734.94</t>
+          <t>46987.95</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>向文</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06/30 13:00:19</t>
+          <t>06/30 13:54:57</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1061,12 +1061,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>38554.22</t>
+          <t>33734.94</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>李志伟</t>
+          <t>马瑞昭</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06/30 10:47:16</t>
+          <t>06/30 13:00:19</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>33734.94</t>
+          <t>38554.22</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>耿振云</t>
+          <t>李志伟</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06/30 10:22:52</t>
+          <t>06/30 10:47:16</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,17 +1140,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>114634.15</t>
+          <t>33734.94</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t/>
+          <t>耿振云</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06/30 10:08:02</t>
+          <t>06/30 10:22:52</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1182,17 +1182,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>114634.15</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06/29 12:46:37</t>
+          <t>06/30 10:08:02</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1229,12 +1229,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>林伟超</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06/27 13:03:05</t>
+          <t>06/29 12:46:37</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1266,17 +1266,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>6172.84</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t/>
+          <t>林伟超</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06/27 11:42:49</t>
+          <t>06/27 13:03:05</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>6172.84</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1335,12 +1335,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06/26 14:40:59</t>
+          <t>06/27 11:42:49</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1377,12 +1377,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06/25 16:34:17</t>
+          <t>06/26 14:40:59</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1392,17 +1392,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>48192.77</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1419,12 +1419,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06/24 12:36:33</t>
+          <t>06/25 16:34:17</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1434,17 +1434,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>21428.57</t>
+          <t>48192.77</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1461,166 +1461,181 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>06/24 12:36:33</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>180000</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>21428.57</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>马瑞昭</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>06/24 12:08:55</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>24096.39</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>羊美云</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="39"/>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="42"/>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="43"/>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/23 12:09:30</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07/22 16:14:19</t>
+          <t>07/23 12:09:30</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>32732</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1642,12 +1657,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07/21 20:19:37</t>
+          <t>07/22 16:14:19</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>32732</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1657,7 +1672,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1669,12 +1684,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07/18 17:18:15</t>
+          <t>07/21 20:19:37</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>10790</t>
+          <t>434</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1684,7 +1699,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1696,12 +1711,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07/17 19:45:53</t>
+          <t>07/18 17:18:15</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>52006</t>
+          <t>10790</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1723,12 +1738,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07/14 20:52:08</t>
+          <t>07/17 19:45:53</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>52006</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1738,7 +1753,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1750,12 +1765,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07/12 18:39:01</t>
+          <t>07/14 20:52:08</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>6407</t>
+          <t>27710</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1777,12 +1792,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07/12 18:26:46</t>
+          <t>07/12 18:39:01</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>6407</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1804,12 +1819,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07/10 18:27:46</t>
+          <t>07/12 18:26:46</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>48049</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1819,7 +1834,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1831,12 +1846,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07/09 11:40:53</t>
+          <t>07/10 18:27:46</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>56483</t>
+          <t>48049</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1858,12 +1873,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07/06 17:52:23</t>
+          <t>07/09 11:40:53</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>56483</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1885,12 +1900,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07/04 17:10:11</t>
+          <t>07/06 17:52:23</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>20238</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1912,12 +1927,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07/02 19:00:39</t>
+          <t>07/04 17:10:11</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>128241</t>
+          <t>20238</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1939,12 +1954,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07/02 12:32:59</t>
+          <t>07/02 19:00:39</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>128241</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1966,12 +1981,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07/01 16:52:50</t>
+          <t>07/02 12:32:59</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>77108</t>
+          <t>27710</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1993,12 +2008,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06/30 15:16:34</t>
+          <t>07/01 16:52:50</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>72289</t>
+          <t>77108</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2020,12 +2035,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>06/30 12:16:11</t>
+          <t>06/30 15:16:34</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>68610</t>
+          <t>72289</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2035,7 +2050,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2047,12 +2062,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>06/30 11:50:16</t>
+          <t>06/30 12:16:11</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>61000</t>
+          <t>68610</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2062,7 +2077,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2074,12 +2089,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>06/30 11:35:36</t>
+          <t>06/30 11:50:16</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>79000</t>
+          <t>61000</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2101,12 +2116,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>06/29 14:04:21</t>
+          <t>06/30 11:35:36</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>79000</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2128,12 +2143,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>06/27 13:07:43</t>
+          <t>06/29 14:04:21</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>42317</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2143,7 +2158,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2155,12 +2170,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>06/26 16:07:20</t>
+          <t>06/27 13:07:43</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>42317</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2170,7 +2185,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2182,12 +2197,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>06/25 19:22:04</t>
+          <t>06/26 16:07:20</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>48192</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2209,83 +2224,110 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
+          <t>06/25 19:22:04</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>48192</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
           <t>06/24 14:10:57</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>45524</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="69"/>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="70"/>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>8435571</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1015495.57</t>
+          <t>8531561</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>1003744</t>
+          <t>1026528.91</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>1003744</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>11751.57</t>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>22784.91</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-all.xlsx
@@ -1630,12 +1630,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07/23 12:09:30</t>
+          <t>07/25 19:36:27</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>22798</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1657,12 +1657,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07/22 16:14:19</t>
+          <t>07/23 12:09:30</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>32732</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1684,12 +1684,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07/21 20:19:37</t>
+          <t>07/22 16:14:19</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>32732</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1711,12 +1711,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07/18 17:18:15</t>
+          <t>07/21 20:19:37</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>10790</t>
+          <t>434</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1738,12 +1738,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07/17 19:45:53</t>
+          <t>07/18 17:18:15</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>52006</t>
+          <t>10790</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1765,12 +1765,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07/14 20:52:08</t>
+          <t>07/17 19:45:53</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>52006</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1792,12 +1792,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07/12 18:39:01</t>
+          <t>07/14 20:52:08</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>6407</t>
+          <t>27710</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1819,12 +1819,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07/12 18:26:46</t>
+          <t>07/12 18:39:01</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>6407</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1846,12 +1846,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07/10 18:27:46</t>
+          <t>07/12 18:26:46</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>48049</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -1873,12 +1873,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07/09 11:40:53</t>
+          <t>07/10 18:27:46</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>56483</t>
+          <t>48049</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1900,12 +1900,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07/06 17:52:23</t>
+          <t>07/09 11:40:53</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>56483</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1927,12 +1927,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07/04 17:10:11</t>
+          <t>07/06 17:52:23</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>20238</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1954,12 +1954,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07/02 19:00:39</t>
+          <t>07/04 17:10:11</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>128241</t>
+          <t>20238</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1981,12 +1981,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07/02 12:32:59</t>
+          <t>07/02 19:00:39</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>128241</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2008,12 +2008,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07/01 16:52:50</t>
+          <t>07/02 12:32:59</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>77108</t>
+          <t>27710</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2035,12 +2035,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>06/30 15:16:34</t>
+          <t>07/01 16:52:50</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>72289</t>
+          <t>77108</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2062,12 +2062,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>06/30 12:16:11</t>
+          <t>06/30 15:16:34</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>68610</t>
+          <t>72289</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2089,12 +2089,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>06/30 11:50:16</t>
+          <t>06/30 12:16:11</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>61000</t>
+          <t>68610</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2116,12 +2116,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>06/30 11:35:36</t>
+          <t>06/30 11:50:16</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>79000</t>
+          <t>61000</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2143,12 +2143,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>06/29 14:04:21</t>
+          <t>06/30 11:35:36</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>79000</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2170,12 +2170,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>06/27 13:07:43</t>
+          <t>06/29 14:04:21</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>42317</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2197,12 +2197,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>06/26 16:07:20</t>
+          <t>06/27 13:07:43</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>42317</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2224,12 +2224,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>06/25 19:22:04</t>
+          <t>06/26 16:07:20</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>48192</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2251,83 +2251,110 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
+          <t>06/25 19:22:04</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>48192</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
           <t>06/24 14:10:57</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>45524</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="70"/>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="71"/>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>8531561</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>1026528.91</t>
+          <t>8531561</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1003744</t>
+          <t>1026528.91</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>1026542</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>22784.91</t>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>-13.09</t>
         </is>
       </c>
     </row>
